--- a/stockpredict/roadmap_version_2.xlsx
+++ b/stockpredict/roadmap_version_2.xlsx
@@ -197,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -289,6 +289,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -768,7 +771,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Overlay Indicators</t>
+          <t>Overlay Indicators ✅</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -792,12 +795,12 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>All use LineSeries / BollingerSeries — same pane, same price scale. No new pane needed.</t>
+          <t>Completed 2026-05-25. BB, VWAP, custom-period SMA — all on price pane.</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1303,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 ✅</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1325,7 +1328,7 @@
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr"/>
@@ -1343,7 +1346,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 ✅</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -1368,7 +1371,7 @@
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr"/>
@@ -1386,7 +1389,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 ✅</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1411,7 +1414,7 @@
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr"/>
@@ -1429,7 +1432,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 ✅</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1454,7 +1457,7 @@
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -2067,7 +2070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2208,6 +2211,49 @@
       <c r="D10" s="29" t="inlineStr"/>
       <c r="E10" s="29" t="inlineStr"/>
       <c r="F10" s="29" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>C-201 Bollinger Bands (20,2)
+C-202 VWAP (anchored cumulative)
+C-203 Custom-period SMA + number input
+C-204 Extended INDICATOR_OPTIONS</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>StockChart.js
+roadmap_version_2.xlsx</t>
+        </is>
+      </c>
+      <c r="E11" s="33" t="inlineStr">
+        <is>
+          <t>Phase 2 done. Production build clean (only pre-existing
+ESLint warnings in unrelated files).
+New indicators default OFF to avoid initial clutter.
+BB tooltip at origin [8,40]; SMA period input in dropdown
+(clamped 2–200).</t>
+        </is>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>Phase 3: Stochastic Oscillator pane (C-301), ATR pane (C-302),
+paneConfig refactor (C-303).
+Tip: refactor hardcoded pane heights into a paneConfig[] array
+first — Phase 3 introduces 2 new panes.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/stockpredict/roadmap_version_2.xlsx
+++ b/stockpredict/roadmap_version_2.xlsx
@@ -812,7 +812,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>More Oscillators</t>
+          <t>More Oscillators ✅</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -835,12 +835,12 @@
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>react-financial-charts has stochasticOscillator() and atr() calculators + series.</t>
+          <t>Completed 2026-05-25. Stochastic (12,3,3) and ATR (14) panes; paneConfig refactor — sub-pane origins computed from SUB_PANE_HEIGHTS + enabled flags. Bottom-most enabled sub-pane shows date tick labels.</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 ✅</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr"/>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 ✅</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 ✅</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -2070,7 +2070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2252,6 +2252,50 @@
 paneConfig refactor (C-303).
 Tip: refactor hardcoded pane heights into a paneConfig[] array
 first — Phase 3 introduces 2 new panes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>C-303 paneConfig refactor (SUB_PANE_HEIGHTS + paneOrigin lookup)
+C-301 Stochastic Oscillator pane (12,3,3) with %K/%D + tooltip
+C-302 ATR (14) pane — LineSeries + SingleValueTooltip</t>
+        </is>
+      </c>
+      <c r="D12" s="33" t="inlineStr">
+        <is>
+          <t>StockChart.js
+roadmap_version_2.xlsx</t>
+        </is>
+      </c>
+      <c r="E12" s="33" t="inlineStr">
+        <is>
+          <t>Phase 3 done. Same session as Phase 2.
+Refactor first: hardcoded macdHeight/volHeight replaced with
+SUB_PANE_HEIGHTS={macd,stoch,atr,volume} and computed paneOrigin.
+Bottom-most enabled sub-pane now owns the date tick labels +
+MouseCoordinateX (previously only volume showed them).
+Stochastic and ATR default OFF.
+Production build clean (+771 B gzipped).</t>
+        </is>
+      </c>
+      <c r="F12" s="33" t="inlineStr">
+        <is>
+          <t>Phase 4: Drawing tools — trend line (C-401), horizontal S/R (C-402),
+Fibonacci (C-403), drawing toolbar UI (C-404).
+Requires @react-financial-charts/interactive (already bundled in v2).
+New DrawingToolbar.js component + persisted drawings array state.</t>
         </is>
       </c>
     </row>

--- a/stockpredict/roadmap_version_2.xlsx
+++ b/stockpredict/roadmap_version_2.xlsx
@@ -893,7 +893,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Chart Enhancements</t>
+          <t>Chart Enhancements ✅</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Heikin-Ashi uses heikinAshi() calculator. localStorage key per stock symbol.</t>
+          <t>Completed 2026-05-25. Timeframe tabs (1M/3M/6M/1Y/All), candle/Heikin-Ashi/OHLC-bar toggle, localStorage per-symbol prefs, HoverTooltip with all active values.</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 ✅</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr"/>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 ✅</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr"/>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 ✅</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 ✅</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr"/>
@@ -2070,7 +2070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2296,6 +2296,59 @@
 Fibonacci (C-403), drawing toolbar UI (C-404).
 Requires @react-financial-charts/interactive (already bundled in v2).
 New DrawingToolbar.js component + persisted drawings array state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>C-501 Timeframe tabs (1M/3M/6M/1Y/All) — internal slice
+C-502 Candle / Heikin-Ashi / OHLC Bar toggle (HA computed manually
+       into haOpen/haHigh/haLow/haClose so candles toggle non-
+       destructively and indicators keep using real OHLC)
+C-503 Per-symbol localStorage prefs (indicators, smaPeriod,
+       timeframe, candleType) keyed by stockchart_prefs_{symbol}
+C-504 HoverTooltip on price pane — OHLC + all active indicators</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="inlineStr">
+        <is>
+          <t>StockChart.js
+CompanyCharts.js (pass symbol prop)
+roadmap_version_2.xlsx</t>
+        </is>
+      </c>
+      <c r="E13" s="33" t="inlineStr">
+        <is>
+          <t>Phase 5 done. Same session as Phases 2 + 3.
+When a timeframe other than "All" is selected, the initial x-window
+fits the whole sliced range (not the legacy 100-row window).
+CompanyCharts already had outer 1W/1M/1Y/5Y buttons — left in place;
+inner tabs further slice whatever the parent passes. Slight
+duplication but no regression. Cleanup is a UX task for later.
+Bundle: +2.84 kB gzipped.</t>
+        </is>
+      </c>
+      <c r="F13" s="33" t="inlineStr">
+        <is>
+          <t>Phase 4: Drawing tools. Imports from
+@react-financial-charts/interactive: TrendLine,
+EquidistantChannel/StraightLine for H-line, FibonacciRetracement,
+plus new DrawingToolbar.js component.
+Decisions to make on entry:
+  • toolbar position (left rail vs. top-right next to dropdown)
+  • drawings persistence: state-only vs. localStorage per symbol
+  • default active tool: cursor (recommended)</t>
         </is>
       </c>
     </row>

--- a/stockpredict/roadmap_version_2.xlsx
+++ b/stockpredict/roadmap_version_2.xlsx
@@ -852,7 +852,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Interactive Drawing Tools</t>
+          <t>Interactive Drawing Tools ✅</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Uses @react-financial-charts/interactive (TrendLine, FibonacciRetracement, etc). Coordinates saved in component state.</t>
+          <t>Completed 2026-05-25. TrendLine + InteractiveYCoordinate (H-line) + FibonacciRetracement wired into price pane. DrawingToolbar in header. Per-symbol persistence in localStorage. Clear-all action; per-item delete only on H-line.</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 ✅</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr"/>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 ✅</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 ✅</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 ✅</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
@@ -2070,7 +2070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2349,6 +2349,57 @@
   • toolbar position (left rail vs. top-right next to dropdown)
   • drawings persistence: state-only vs. localStorage per symbol
   • default active tool: cursor (recommended)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B14" s="33" t="inlineStr">
+        <is>
+          <t>Phase 4</t>
+        </is>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>C-404 New DrawingToolbar.js with cursor/trend/hline/fib + Clear-all
+C-401 TrendLine wired with state-driven trends[] array
+C-402 InteractiveYCoordinate for horizontal S/R lines:
+       onChoosePosition adds, onDragComplete moves, onDelete removes
+C-403 FibonacciRetracement (BOUND type) wired with retracements[]
+Drawings persisted per symbol under stockchart_drawings_{symbol}</t>
+        </is>
+      </c>
+      <c r="D14" s="33" t="inlineStr">
+        <is>
+          <t>StockChart.js
+DrawingToolbar.js (new)
+roadmap_version_2.xlsx</t>
+        </is>
+      </c>
+      <c r="E14" s="33" t="inlineStr">
+        <is>
+          <t>Phase 4 done. Same session as Phases 2 + 3 + 5.
+Toolbar position: top-left next to timeframe/candle tabs.
+Default tool: cursor (chart starts in pan/zoom mode).
+Per-item delete: only H-line via onDelete callback. Trend/Fib
+rely on Clear-all (DrawingObjectSelector wiring is a future polish).
+Bundle: +7.78 kB gzipped (interactive package is the heavyweight).</t>
+        </is>
+      </c>
+      <c r="F14" s="33" t="inlineStr">
+        <is>
+          <t>All planned phases (1–5) now Done. Phase 6 (Multi-stock comparison)
+remains Not Started — XL effort, flagged future in the roadmap.
+Polish backlog:
+  • DrawingObjectSelector + DEL key for per-item delete
+  • Snap-to-bar option for trend lines (snap={true}+snapTo)
+  • Remove the legacy bootstrap buttons in CompanyCharts (now
+    redundant with the internal timeframe tabs)
+  • Clean up stub Select for "Leanne Graham" / "Ervin Howell"</t>
         </is>
       </c>
     </row>

--- a/stockpredict/roadmap_version_2.xlsx
+++ b/stockpredict/roadmap_version_2.xlsx
@@ -2070,7 +2070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2400,6 +2400,53 @@
   • Remove the legacy bootstrap buttons in CompanyCharts (now
     redundant with the internal timeframe tabs)
   • Clean up stub Select for "Leanne Graham" / "Ervin Howell"</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>Cleanup</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>Removed legacy bootstrap buttons (1w/1m/1y/5y/All) + stub
+react-dropdown-select ("Leanne Graham") from CompanyCharts.js.
+Now redundant after Phase 5 internal timeframe tabs in StockChart.
+Also dropped: periodStockData slicing state, debug console.log,
+unused selectItem/styles/options.</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>CompanyCharts.js</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>Browser-verified Phases 2–5 working end-to-end on port 3004
+(user signed off: "beautiful charts").
+Cleanup: −105 / +26 lines in CompanyCharts.js.
+Bundle: −18 kB gzipped (vs. Phase 4 commit) — bootstrap CSS
+was being imported via this file. react-bootstrap stays as a
+dependency since Solutions/TimeSeries/Agent pages still use it.</t>
+        </is>
+      </c>
+      <c r="F15" s="33" t="inlineStr">
+        <is>
+          <t>Polish backlog remaining:
+  • DrawingObjectSelector + DEL key for per-item drawing delete
+  • Snap-to-bar option for trend lines (snap={true}+snapTo)
+  • Misleading "demo / password" hint on login screen (server
+    rejects with 422 — email field validated as email)
+  • Transient &lt;rect&gt; negative-height SVG warning at chart init
+  • Phase 6 (multi-stock compare) — XL, still Not Started</t>
         </is>
       </c>
     </row>

--- a/stockpredict/roadmap_version_2.xlsx
+++ b/stockpredict/roadmap_version_2.xlsx
@@ -2070,7 +2070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2447,6 +2447,48 @@
     rejects with 422 — email field validated as email)
   • Transient &lt;rect&gt; negative-height SVG warning at chart init
   • Phase 6 (multi-stock compare) — XL, still Not Started</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>Cleanup</t>
+        </is>
+      </c>
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>Removed misleading "Demo account: demo/password" hint from LoginForm.</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>LoginForm.js
+auth.css
+en.json / vi.json</t>
+        </is>
+      </c>
+      <c r="E16" s="33" t="inlineStr">
+        <is>
+          <t>Hint was broken: auth-service validates the username field as an
+email and rejected "demo" with 422. No demo user was seeded.
+Removed JSX block, .auth-demo / .auth-demo-text CSS rules, and
+login.demo_account translation keys in both locales.
+Bundle: −92 B gzipped (JS), −41 B (CSS).</t>
+        </is>
+      </c>
+      <c r="F16" s="33" t="inlineStr">
+        <is>
+          <t>Polish backlog still open:
+  • DrawingObjectSelector + DEL key for per-item drawing delete
+  • Snap-to-bar for trend lines
+  • Transient &lt;rect&gt; negative-height SVG warning at chart init
+  • Phase 6 (multi-stock compare)</t>
         </is>
       </c>
     </row>

--- a/stockpredict/roadmap_version_2.xlsx
+++ b/stockpredict/roadmap_version_2.xlsx
@@ -11,6 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart Tasks" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Session Log" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API Reference" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CD Overview" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CD Tasks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CD Architecture" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,6 +100,16 @@
       <color rgb="00375623"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Courier New"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C55A11"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -171,7 +184,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -193,11 +206,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -294,6 +351,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2070,7 +2162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2489,6 +2581,76 @@
   • Snap-to-bar for trend lines
   • Transient &lt;rect&gt; negative-height SVG warning at chart init
   • Phase 6 (multi-stock compare)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Chart Decomp (CD-2 / CD-3 / CD-4)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CD-2: chart-decomp-service FastAPI microservice
+  • Port 8011, Traefik PathPrefix /stock_helper/api/v2/chart-decomp
+  • 13 endpoints: POST /decompose/{modwt,emd,eemd,vmd}, /time-freq/{cwt,hht}, /hurst, /coherence,
+    /forecast/{har,vmd-har,compare}, /realized-vol, /backtest/vol-target
+  • Library smoke-test on startup; /health/ready returns 503 if it fails
+  • Dockerfile installs stock-common + chart-decomp-lib with -e
+  • docker-compose.yml entry + Traefik labels added
+CD-3: ChartDecomp frontend viewer (src/components/Pages/ChartDecomp/index.js)
+  • Route /chart-decomp — 4 tabs: Decomp, Time-Freq, Hurst, Forecast
+  • InputPanel: ticker picker + 512-pt AR(1)+harmonic demo generator
+  • ComponentChart: stacked recharts LineChart with optional COI markers
+  • ScalogramCanvas: HTML5 canvas Viridis heatmap with COI mask
+  • HurstTab: Ĥ estimate + regime label + log₂-variance chart
+  • ForecastTab: walk-forward HAR/VMD-HAR comparison + metric cards
+  • Bilingual vi/en i18n (~90 new keys per locale)
+CD-4: VolForecastPage (src/components/Pages/ChartDecomp/VolForecastPage.js)
+  • Route /vol-forecast — 3 panels: Data, Compare, Backtest
+  • ComparePanel: HAR vs VMD-HAR with DM-stat badge (green if &gt;1.96),
+    winner banner (C4: ΔRMSE+ΔQLIKE+DM&gt;1.96 all required), metric delta table
+  • BacktestPanel: vol-targeting equity curve + drawdown + positions + turnover
+  • pricesToLogRV / logRVToAnnVol utilities; 756-day demo path
+  • POST /forecast/compare backend endpoint (single round-trip for DM test)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>stock_microservices/services/chart-decomp-service/ (new)
+stock_microservices/chart-decomp-lib/ (new)
+stock_microservices/docker-compose.yml
+src/components/Pages/ChartDecomp/index.js (new)
+src/components/Pages/ChartDecomp/VolForecastPage.js (new)
+src/services/chartDecompService.js (new)
+src/constants/api.js (+14 CHART_DECOMP_* endpoints)
+src/components/Layout/MainLayout.js (2 new routes)
+src/components/Layout/Sidebar.js (chart-decomp + vol-forecast submenu)
+src/i18n/locales/vi.json + en.json (+150 keys each)
+SRS_chart_decomposition.md (new)
+roadmap_version_2.xlsx</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>CD-1 through CD-4 fully implemented.
+CD-5: test files CD-501..505 exist (unit/statistical/causality);
+  CD-506 (test_e2e_heston.py) not yet written — marked Partial.
+Known fix applied in CD-2: facade kwargs (not params objects);
+  HurstResult.H / .variances fields; split refit_vmd_every/refit_model_every.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CD-5 test_e2e_heston.py — 2500-day Heston SV path end-to-end test.
+Verify CD-3 and CD-4 pages in browser once backend is running.
+Consider npm run build to check for any remaining import/TS issues.</t>
         </is>
       </c>
     </row>
@@ -2880,4 +3042,2606 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Chart Decomposition Module — Phase Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SRS: SRS_chart_decomposition.md  |  As of 2026-05-27  |  Status: CD-1 Done | CD-2 Done | CD-3 Done | CD-4 Done | CD-5 Partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Key Deliverables</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Primary Files / Libs</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Duration Est.</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="110" customHeight="1">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>CD-1</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Backend Library
+(Python)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>• MODWTResult, EMDResult, VMDResult, TimeFreqResult, CoherenceResult dataclasses
+• modwt(), emd(), eemd(), vmd() decomposition functions
+• cwt_scalogram(), hilbert_spectrum() time-frequency views
+• hurst_wavelet() long-memory estimator
+• wavelet_coherence() bivariate analysis
+• realized_variance() / realized_vol() RV computation
+• Hybrid pipelines A (wavelet-denoise→EMD), B (EMD→CWT), C (MODWT→Hilbert)
+• NFR: &lt; 100 ms MODWT, &lt; 2 s VMD on len-1024</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="inlineStr">
+        <is>
+          <t>chart_decomp/
+  decomp.py
+  time_freq.py
+  hurst.py
+  coherence.py
+  realized_vol.py
+  pipelines.py
+  types.py
+Libs: PyWavelets, PyEMD,
+vmdpy, SciPy, NumPy</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="F5" s="36" t="inlineStr">
+        <is>
+          <t>6–8 days</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Pure-Python library with no web layer. Must satisfy causality constraint C1 (no look-ahead). All stochastic functions accept seed=. NFR-R1: input validation before algorithm. See Appendix B for implementation traps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="110" customHeight="1">
+      <c r="A6" s="37" t="inlineStr">
+        <is>
+          <t>CD-2</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>FastAPI Microservice
+(chart-decomp-service)</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>• FastAPI app skeleton: /health/live, /health/ready, /metrics
+• POST /decompose/{modwt,emd,eemd,vmd,cwt,hht}
+• POST /hurst, POST /coherence
+• POST /forecast/{har,vmd-har}
+• POST /backtest/vol-target
+• CLI: chart-decompose decompose|hurst|forecast|backtest
+• Traefik label + compose entry on port 8011
+• Docker image + requirements</t>
+        </is>
+      </c>
+      <c r="D6" s="35" t="inlineStr">
+        <is>
+          <t>stock_microservices/services/
+  chart-decomp-service/
+    app/
+      main.py
+      config.py
+      api/routes.py
+      services/
+    Dockerfile
+    requirements.txt
+chart_decomp/ (lib, installed -e)
+docker-compose.yml (add service)</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F6" s="36" t="inlineStr">
+        <is>
+          <t>2–3 days</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Thin HTTP wrapper around the chart_decomp library. Endpoints accept JSON arrays (user supplies data — per SRS §1.2). Large responses (scalogram arrays) should use streaming or numpy npz. Register /chart-decomp path prefix in Traefik.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="110" customHeight="1">
+      <c r="A7" s="38" t="inlineStr">
+        <is>
+          <t>CD-3</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Frontend — Decomposition
+Viewer</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>• Route: /chart-decomposition
+• SeriesInputPanel: stock symbol picker OR CSV upload
+• MODWTBandChart: stacked line charts (approx + D1–DJ)
+• CWTScalogram: heatmap, log-period y-axis, COI dashed overlay
+• HilbertSpectrum: Hilbert spectrum heatmap
+• HurstDiagnostics: log-log variance plot + Ĥ readout
+• WaveletCoherence: R² heatmap with phase arrows
+• Sidebar nav entry + en/vi i18n keys</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="inlineStr">
+        <is>
+          <t>stock_react_javascript/stock-react-app/src/
+  pages/ChartDecomposition/
+    index.js
+    SeriesInputPanel.js
+    MODWTBandChart.js
+    CWTScalogram.js
+    HilbertSpectrum.js
+    HurstDiagnostics.js
+    CoherenceHeatmap.js
+  services/chartDecompService.js
+  constants/api.js (add endpoints)</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="F7" s="36" t="inlineStr">
+        <is>
+          <t>5–7 days</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Heatmaps via recharts or d3. COI overlay must be rendered on all time-freq plots (NFR constraint B7). Phase arrows on coherence plot only where R² &gt; 0.6 and outside COI. All API calls go through chartDecompService.js (no direct axios in components).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="110" customHeight="1">
+      <c r="A8" s="39" t="inlineStr">
+        <is>
+          <t>CD-4</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Frontend — Forecasting
+&amp; Backtest UI</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>• ForecastPanel: HAR vs VMD-HAR line chart overlaid with actuals
+• MetricsTable: RMSE, MAE, R², QLIKE, DM-stat side-by-side
+• BacktestEquityCurve: net PnL vs buy-and-hold vs naive vol-target
+• RollingVolChart: 30-day rolling strategy vol vs target line
+• PositionChart: position size over time
+• StrategyMetricsCard: Sharpe, MaxDD, turnover, cost drag</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="inlineStr">
+        <is>
+          <t>stock_react_javascript/stock-react-app/src/
+  pages/ChartDecomposition/
+    ForecastPanel.js
+    MetricsTable.js
+    BacktestEquityCurve.js
+    RollingVolChart.js
+    StrategyMetricsCard.js</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F8" s="36" t="inlineStr">
+        <is>
+          <t>3–4 days</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Forecast chart must label model as 'improves on HAR' only when all three conditions pass (ΔRMSE &gt; 0, ΔQLIKE &gt; 0, |DM| &gt; 1.96) — per SRS §3.7.3. Backtest starts after minimum training window (no equity curve in burn-in).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="110" customHeight="1">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>CD-5</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Testing &amp; Validation</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>• Unit: round-trip reconstruction (MODWT 1e-10, EMD 1e-6, VMD 0.2 rel)
+• Unit: MODWT translation invariance
+• Unit: VMD mode count + ascending center-freq sort
+• Unit: edge robustness (N=100, 257, 1024, 5000)
+• Statistical: Hurst on fGn H∈{0.3,0.5,0.7,0.85}, N=4096, err≤0.07
+• Statistical: wavelet coherence validation (known-construction pair)
+• Causality: no-leakage swap test
+• Causality: deliberate look-ahead detector
+• E2E: 2500-day Heston SV path, HAR R²≥0.85 OOS,
+  rolling-vol within ±30% target on ≥70% days</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="inlineStr">
+        <is>
+          <t>stock_microservices/services/chart-decomp-service/
+  tests/
+    test_decomp.py
+    test_time_freq.py
+    test_hurst.py
+    test_coherence.py
+    test_forecast.py
+    test_causality.py
+    test_e2e_heston.py</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F9" s="36" t="inlineStr">
+        <is>
+          <t>2–3 days</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>All stochastic tests use fixed seeds for reproducibility (NFR-RP1). E2E Heston test is marked @pytest.mark.slow and excluded from quick-test.sh. The look-ahead regression test must run in CI to guard against accidental leakage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="41" t="inlineStr">
+        <is>
+          <t>Total estimate (new module end-to-end)</t>
+        </is>
+      </c>
+      <c r="B10" s="45" t="n"/>
+      <c r="C10" s="45" t="n"/>
+      <c r="D10" s="46" t="n"/>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="42" t="inlineStr">
+        <is>
+          <t>18–25 days</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Assumes one developer. CD-1 and CD-3 can partially overlap once decomposition API shapes are agreed. CD-5 runs in parallel with CD-4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>Effort key:</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>S = &lt;2 h</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>M = 2–4 h</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>L = 4–8 h</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>XL = &gt;8 h</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Chart Decomposition — Detailed Task List</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Ref: SRS_chart_decomposition.md  |  2026-05-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Component / File</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Key API / Symbol</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Depends On</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Notes / Pitfalls</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>CD-101</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>CD-1</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>Data-class result types</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="inlineStr">
+        <is>
+          <t>chart_decomp/types.py</t>
+        </is>
+      </c>
+      <c r="E5" s="35" t="inlineStr">
+        <is>
+          <t>MODWTResult, EMDResult, VMDResult,
+TimeFreqResult, CoherenceResult,
+ForecastResult, BacktestResult</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Define all @dataclass types from SRS §4.1 first — they are the contract between backend modules and the API layer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>CD-102</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>CD-1</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>MODWT decomposition (FR-DECOMP-MODWT)</t>
+        </is>
+      </c>
+      <c r="D6" s="35" t="inlineStr">
+        <is>
+          <t>chart_decomp/decomp.py
+→ modwt()</t>
+        </is>
+      </c>
+      <c r="E6" s="35" t="inlineStr">
+        <is>
+          <t>pywt.swt(norm=True), sym8,
+pad to next power-of-2,
+COI width = (2^j-1)*(L-1)</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>CD-101</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Pad to 2^n, run SWT, trim back. Symmetric boundary default. Return [A_J, D_J, …, D_1] — all length N. Must satisfy round-trip to 1e-10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>CD-103</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>CD-1</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>EMD &amp; EEMD decomposition (FR-DECOMP-EMD)</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="inlineStr">
+        <is>
+          <t>chart_decomp/decomp.py
+→ emd(), eemd()</t>
+        </is>
+      </c>
+      <c r="E7" s="35" t="inlineStr">
+        <is>
+          <t>PyEMD.EMD, PyEMD.EEMD,
+n_trials=100, noise_width=0.2*std(x),
+period = 2*N/n_zero_crossings</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>CD-101</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Sort IMFs highest→lowest freq (period ascending). Report dominant_periods. EEMD uses seed for noise perturbation (NFR-RP1). Trap B3: end effects — do not use final edge values in forecasting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>CD-104</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>CD-1</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>VMD decomposition (FR-DECOMP-VMD)</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="inlineStr">
+        <is>
+          <t>chart_decomp/decomp.py
+→ vmd()</t>
+        </is>
+      </c>
+      <c r="E8" s="35" t="inlineStr">
+        <is>
+          <t>vmdpy.VMD, K=5, alpha=1500,
+sort by center_freq ascending,
+subtract/restore mean</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>CD-101</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Sort modes by center frequency at every call (Trap B2). Report relative L2 reconstruction error. Trap B4: VMD is not exact reconstruction — do not interpret variance shares as 100%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>CD-105</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>CD-1</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>CWT scalogram (FR-TF-CWT)</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="inlineStr">
+        <is>
+          <t>chart_decomp/time_freq.py
+→ cwt_scalogram()</t>
+        </is>
+      </c>
+      <c r="E9" s="35" t="inlineStr">
+        <is>
+          <t>pywt.cwt, cmor1.5-1.0,
+scales=geomspace(2,256,64),
+COI boundary array</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>CD-101</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Return |W|², phase angle(W), COI as 1-D array indexed by time. COI = sqrt(2)*scale in samples for Morlet. Trap B7: COI must always be returned; plotting function must overlay it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>CD-106</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>CD-1</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Hilbert spectrum / HHT (FR-TF-HHT)</t>
+        </is>
+      </c>
+      <c r="D10" s="35" t="inlineStr">
+        <is>
+          <t>chart_decomp/time_freq.py
+→ hilbert_spectrum()</t>
+        </is>
+      </c>
+      <c r="E10" s="35" t="inlineStr">
+        <is>
+          <t>scipy.signal.hilbert,
+instantaneous freq via phase unwrapping,
+Gaussian smoothing sigma=(1.5,4)</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>CD-101</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Works on both EMD IMFs and MODWT detail bands. Accumulate A(t)² at bin f(t) per (component, time). Configurable Gaussian smoothing before return.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>CD-107</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>CD-1</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Hurst exponent via wavelet variance (FR-HURST)</t>
+        </is>
+      </c>
+      <c r="D11" s="35" t="inlineStr">
+        <is>
+          <t>chart_decomp/hurst.py
+→ hurst_wavelet()</t>
+        </is>
+      </c>
+      <c r="E11" s="35" t="inlineStr">
+        <is>
+          <t>MODWT Var(d_j) per level,
+regress log2_var on j,
+H = (slope+2)/2</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>CD-102</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>j_range=(2,8) by default — drops finest and coarsest scales. Return Ĥ, slope, intercept, full variance array, scale mask. Must pass statistical test: error ≤ 0.07 on fGn H∈{0.3,0.5,0.7,0.85}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>CD-108</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t>CD-1</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Wavelet coherence (FR-COH)</t>
+        </is>
+      </c>
+      <c r="D12" s="35" t="inlineStr">
+        <is>
+          <t>chart_decomp/coherence.py
+→ wavelet_coherence()</t>
+        </is>
+      </c>
+      <c r="E12" s="35" t="inlineStr">
+        <is>
+          <t>CWT W_x, W_y, cross-wavelet W_xy,
+smooth in time (Gaussian σ∝scale),
+R²=|S(W_xy)|²/(S(|Wx|²)·S(|Wy|²))</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>CD-105</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>R² bounded [0,1]. Return phase array angle(S(W_xy)). Plot helper: phase arrows only where R²&gt;0.6 and outside COI. Arrows: right=in-phase, left=anti, up=y-leads, down=x-leads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>CD-109</t>
+        </is>
+      </c>
+      <c r="B13" s="34" t="inlineStr">
+        <is>
+          <t>CD-1</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Realized variance / vol (FR-RV)</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="inlineStr">
+        <is>
+          <t>chart_decomp/realized_vol.py
+→ realized_variance(), realized_vol()</t>
+        </is>
+      </c>
+      <c r="E13" s="35" t="inlineStr">
+        <is>
+          <t>RV=sum(r_intraday²),
+log_rv=log(RV+eps),
+annualization=252</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>CD-101</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Accept 2-D (days×intraday) or 1-D daily returns. Warn when 1-D is passed (r² is high-noise estimator). Return RV, vol, log_rv arrays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>CD-110</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>CD-1</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Hybrid pipelines A, B, C (FR-HYB-*)</t>
+        </is>
+      </c>
+      <c r="D14" s="35" t="inlineStr">
+        <is>
+          <t>chart_decomp/pipelines.py
+→ hybrid_a(), hybrid_b(), hybrid_c()</t>
+        </is>
+      </c>
+      <c r="E14" s="35" t="inlineStr">
+        <is>
+          <t>Hybrid A: wavelet-denoise→EMD
+Hybrid B: EMD→CWT-per-IMF
+Hybrid C: MODWT→Hilbert</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>CD-102,CD-103,CD-105,CD-106</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Hybrid A: zero finest k_drop=2 detail bands before EMD. Hybrid B: one CWT per IMF — detect residual mode mixing. Hybrid C: production-friendly (no mode mixing, fully reproducible).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>CD-201</t>
+        </is>
+      </c>
+      <c r="B15" s="37" t="inlineStr">
+        <is>
+          <t>CD-2</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Service skeleton (health, config, metrics, Docker)</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
+        <is>
+          <t>services/chart-decomp-service/
+  app/main.py
+  app/config.py
+  Dockerfile
+  requirements.txt</t>
+        </is>
+      </c>
+      <c r="E15" s="35" t="inlineStr">
+        <is>
+          <t>/health/live, /health/ready,
+/metrics (Prometheus),
+pydantic-settings config</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>CD-101</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Follow existing service shape (see CLAUDE.md §Service shape). Port 8011. Add to docker-compose.yml with Traefik label PathPrefix=/stock_helper/api/v2/chart-decomp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>CD-202</t>
+        </is>
+      </c>
+      <c r="B16" s="37" t="inlineStr">
+        <is>
+          <t>CD-2</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>Decomposition API endpoints</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="inlineStr">
+        <is>
+          <t>services/chart-decomp-service/
+  app/api/routes.py</t>
+        </is>
+      </c>
+      <c r="E16" s="35" t="inlineStr">
+        <is>
+          <t>POST /decompose/modwt
+POST /decompose/emd
+POST /decompose/eemd
+POST /decompose/vmd
+POST /decompose/cwt
+POST /decompose/hht</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>CD-201,CD-102,CD-103,CD-104,CD-105,CD-106</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Request body: {series: float[], params: {...}}. Response: serialised dataclass (numpy arrays as nested lists or base64 npz). Validate input length, dtype, NaN (NFR-R1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>CD-203</t>
+        </is>
+      </c>
+      <c r="B17" s="37" t="inlineStr">
+        <is>
+          <t>CD-2</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>Hurst &amp; Coherence endpoints</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="inlineStr">
+        <is>
+          <t>services/chart-decomp-service/
+  app/api/routes.py</t>
+        </is>
+      </c>
+      <c r="E17" s="35" t="inlineStr">
+        <is>
+          <t>POST /hurst
+POST /coherence</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>CD-201,CD-107,CD-108</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Coherence endpoint accepts two series of equal length. Return COI in response so frontend can overlay it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>CD-204</t>
+        </is>
+      </c>
+      <c r="B18" s="37" t="inlineStr">
+        <is>
+          <t>CD-2</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>Forecasting &amp; Backtest endpoints + HAR/VMD-HAR engine</t>
+        </is>
+      </c>
+      <c r="D18" s="35" t="inlineStr">
+        <is>
+          <t>services/chart-decomp-service/
+  app/api/routes.py
+  app/services/forecast.py
+  app/services/backtest.py</t>
+        </is>
+      </c>
+      <c r="E18" s="35" t="inlineStr">
+        <is>
+          <t>POST /forecast/har
+POST /forecast/vmd-har
+POST /backtest/vol-target
+har_forecast(), vmd_har_forecast()
+vol_target_backtest()</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>CD-201,CD-109,CD-104</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>HAR features: [log_rv[t], mean(t-4:t+1), mean(t-21:t+1)]. VMD-HAR: causal trailing window=1000, edge_lag=5, refit_vmd=20d, refit_model=60d. NFR-R2: raise exception if fit data includes timestamps ≥ prediction time (Trap B1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>CD-205</t>
+        </is>
+      </c>
+      <c r="B19" s="37" t="inlineStr">
+        <is>
+          <t>CD-2</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>CLI: chart-decompose</t>
+        </is>
+      </c>
+      <c r="D19" s="35" t="inlineStr">
+        <is>
+          <t>services/chart-decomp-service/
+  cli.py</t>
+        </is>
+      </c>
+      <c r="E19" s="35" t="inlineStr">
+        <is>
+          <t>chart-decompose decompose
+chart-decompose hurst
+chart-decompose forecast
+chart-decompose backtest</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>CD-202,CD-203,CD-204</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Thin CLI that calls the FastAPI service or library directly. Accept --input CSV, --output npz, --model vmd-har, --target-vol 0.15.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="56" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>CD-301</t>
+        </is>
+      </c>
+      <c r="B20" s="38" t="inlineStr">
+        <is>
+          <t>CD-3</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Route, page layout + sidebar entry + i18n</t>
+        </is>
+      </c>
+      <c r="D20" s="35" t="inlineStr">
+        <is>
+          <t>pages/ChartDecomposition/index.js
+src/constants/api.js
+en.json / vi.json
+Sidebar.js</t>
+        </is>
+      </c>
+      <c r="E20" s="35" t="inlineStr">
+        <is>
+          <t>React Router /chart-decomposition,
+API_ENDPOINTS.CHART_DECOMP,
+i18n keys: chartDecomp.*</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>CD-202</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Follow existing page patterns (see TechnicalAnalysis.js for layout reference). Add nav item under Analysis group in Sidebar. Add EN and VI translations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="56" customHeight="1">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>CD-302</t>
+        </is>
+      </c>
+      <c r="B21" s="38" t="inlineStr">
+        <is>
+          <t>CD-3</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Series input panel (symbol picker + CSV upload)</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="inlineStr">
+        <is>
+          <t>pages/ChartDecomposition/
+  SeriesInputPanel.js</t>
+        </is>
+      </c>
+      <c r="E21" s="35" t="inlineStr">
+        <is>
+          <t>stock-data-service GET /stocks/{symbol}/prices,
+FileReader API for CSV upload</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>CD-301</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Two modes: (1) pick existing stock symbol → fetch daily closes, (2) upload CSV (date,value columns). Validate non-empty series before enabling Decompose button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="56" customHeight="1">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>CD-303</t>
+        </is>
+      </c>
+      <c r="B22" s="38" t="inlineStr">
+        <is>
+          <t>CD-3</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>MODWT band chart (stacked line charts)</t>
+        </is>
+      </c>
+      <c r="D22" s="35" t="inlineStr">
+        <is>
+          <t>pages/ChartDecomposition/
+  MODWTBandChart.js</t>
+        </is>
+      </c>
+      <c r="E22" s="35" t="inlineStr">
+        <is>
+          <t>recharts ComposedChart or
+d3 multi-panel SVG,
+scale labels: D1 (1-2d) … DJ (64-128d), Approx</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>CD-302,CD-202</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>One sub-chart per band, same x-axis (date). Label each band with period range. Shade COI region in light grey so users see boundary-affected zones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>CD-304</t>
+        </is>
+      </c>
+      <c r="B23" s="38" t="inlineStr">
+        <is>
+          <t>CD-3</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>CWT scalogram heatmap (log-period y-axis + COI overlay)</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="inlineStr">
+        <is>
+          <t>pages/ChartDecomposition/
+  CWTScalogram.js</t>
+        </is>
+      </c>
+      <c r="E23" s="35" t="inlineStr">
+        <is>
+          <t>d3 colorScale for |W|²,
+log-scale y-axis (period),
+COI as SVG path dashed line</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>CD-302,CD-202</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>Trap B7: COI is mandatory. Dashed line must clearly separate reliable from edge-contaminated region. Power colormap: viridis or plasma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="56" customHeight="1">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>CD-305</t>
+        </is>
+      </c>
+      <c r="B24" s="38" t="inlineStr">
+        <is>
+          <t>CD-3</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Hilbert spectrum heatmap</t>
+        </is>
+      </c>
+      <c r="D24" s="35" t="inlineStr">
+        <is>
+          <t>pages/ChartDecomposition/
+  HilbertSpectrum.js</t>
+        </is>
+      </c>
+      <c r="E24" s="35" t="inlineStr">
+        <is>
+          <t>Same heatmap component as CWT scalogram,
+frequency bins on y-axis</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>CD-302,CD-202</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Reuse heatmap rendering from CWTScalogram. Frequency bins on y-axis (not period). Tooltip shows instantaneous frequency at cursor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>CD-306</t>
+        </is>
+      </c>
+      <c r="B25" s="38" t="inlineStr">
+        <is>
+          <t>CD-3</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>Hurst diagnostics panel</t>
+        </is>
+      </c>
+      <c r="D25" s="35" t="inlineStr">
+        <is>
+          <t>pages/ChartDecomposition/
+  HurstDiagnostics.js</t>
+        </is>
+      </c>
+      <c r="E25" s="35" t="inlineStr">
+        <is>
+          <t>recharts ScatterChart,
+log-log axes,
+LinearRegression fit line</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>CD-302,CD-203</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Plot Var(d_j) vs scale j on log-log axes. Overlay fitted line. Show Ĥ ± SE as prominent readout. Explain interpretation: H&lt;0.5=mean-revert, H=0.5=random walk, H&gt;0.5=trending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="56" customHeight="1">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>CD-307</t>
+        </is>
+      </c>
+      <c r="B26" s="38" t="inlineStr">
+        <is>
+          <t>CD-3</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Wavelet coherence heatmap with phase arrows</t>
+        </is>
+      </c>
+      <c r="D26" s="35" t="inlineStr">
+        <is>
+          <t>pages/ChartDecomposition/
+  CoherenceHeatmap.js</t>
+        </is>
+      </c>
+      <c r="E26" s="35" t="inlineStr">
+        <is>
+          <t>R² heatmap, phase arrows as SVG,
+threshold=0.6, arrow directions</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>CD-302,CD-203</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>Second series picker alongside main series. Phase arrows: right=in-phase, left=anti, up=y-leads, down=x-leads. Only draw arrows outside COI and where R²&gt;0.6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="56" customHeight="1">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>CD-308</t>
+        </is>
+      </c>
+      <c r="B27" s="38" t="inlineStr">
+        <is>
+          <t>CD-3</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>chartDecompService.js API wrapper</t>
+        </is>
+      </c>
+      <c r="D27" s="35" t="inlineStr">
+        <is>
+          <t>src/services/chartDecompService.js</t>
+        </is>
+      </c>
+      <c r="E27" s="35" t="inlineStr">
+        <is>
+          <t>httpClient wrapping all
+POST /decompose/* and
+/hurst /coherence endpoints</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>CD-301</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>Follow existing pattern: one class, one method per endpoint. No direct axios in components. Handle 422 validation errors gracefully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="56" customHeight="1">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>CD-401</t>
+        </is>
+      </c>
+      <c r="B28" s="39" t="inlineStr">
+        <is>
+          <t>CD-4</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>HAR vs VMD-HAR forecast chart</t>
+        </is>
+      </c>
+      <c r="D28" s="35" t="inlineStr">
+        <is>
+          <t>pages/ChartDecomposition/
+  ForecastPanel.js</t>
+        </is>
+      </c>
+      <c r="E28" s="35" t="inlineStr">
+        <is>
+          <t>recharts LineChart,
+Actuals + HAR + VMD-HAR lines,
+OOS window shaded</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>CD-301,CD-204</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>Show OOS window shaded in light blue. Only label VMD-HAR as 'Improves on HAR' if all 3 DM conditions pass (§3.7.3). Include training burn-in period as greyed-out region.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="56" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>CD-402</t>
+        </is>
+      </c>
+      <c r="B29" s="39" t="inlineStr">
+        <is>
+          <t>CD-4</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>OOS metrics comparison table</t>
+        </is>
+      </c>
+      <c r="D29" s="35" t="inlineStr">
+        <is>
+          <t>pages/ChartDecomposition/
+  MetricsTable.js</t>
+        </is>
+      </c>
+      <c r="E29" s="35" t="inlineStr">
+        <is>
+          <t>RMSE, MAE, R², QLIKE, DM-stat,
+conditional colour formatting</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>CD-401</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>Three columns: Naive / HAR / VMD-HAR. Green cell when model beats prior column. Show DM p-value alongside stat; highlight if |DM|&gt;1.96.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="56" customHeight="1">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>CD-403</t>
+        </is>
+      </c>
+      <c r="B30" s="39" t="inlineStr">
+        <is>
+          <t>CD-4</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>Backtest equity curve chart</t>
+        </is>
+      </c>
+      <c r="D30" s="35" t="inlineStr">
+        <is>
+          <t>pages/ChartDecomposition/
+  BacktestEquityCurve.js</t>
+        </is>
+      </c>
+      <c r="E30" s="35" t="inlineStr">
+        <is>
+          <t>recharts AreaChart,
+Net PnL + Buy-and-hold + Naive vol-target,
+Drawdown shaded</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>CD-301,CD-204</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>Three series: net PnL (strategy), buy-and-hold, naive vol-target. Shade max-drawdown period in light red. Start equity curve at end of training window only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="56" customHeight="1">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>CD-404</t>
+        </is>
+      </c>
+      <c r="B31" s="39" t="inlineStr">
+        <is>
+          <t>CD-4</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>Rolling vol chart + strategy metrics card</t>
+        </is>
+      </c>
+      <c r="D31" s="35" t="inlineStr">
+        <is>
+          <t>pages/ChartDecomposition/
+  RollingVolChart.js
+  StrategyMetricsCard.js</t>
+        </is>
+      </c>
+      <c r="E31" s="35" t="inlineStr">
+        <is>
+          <t>30d rolling std of daily PnL,
+target ±30% band lines,
+Sharpe/MaxDD/turnover/cost-drag</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>CD-403</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>Rolling vol chart: dashed target line, light-blue band ±30%. Metrics card: annualized return &amp; vol, Sharpe, MaxDD, avg leverage, annualized turnover, cost drag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="56" customHeight="1">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>CD-501</t>
+        </is>
+      </c>
+      <c r="B32" s="40" t="inlineStr">
+        <is>
+          <t>CD-5</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>Decomposition unit tests (round-trip, edge robustness)</t>
+        </is>
+      </c>
+      <c r="D32" s="35" t="inlineStr">
+        <is>
+          <t>tests/test_decomp.py</t>
+        </is>
+      </c>
+      <c r="E32" s="35" t="inlineStr">
+        <is>
+          <t>MODWT tol=1e-10, EMD tol=1e-6,
+VMD rel_err&lt;0.2,
+N∈{100,257,1024,5000}</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>CD-102,CD-103,CD-104</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>Test round-trip: sum(components) ≈ x within tolerance. Test edge robustness: all lengths complete without error. Test VMD: K modes returned, sorted by ascending center frequency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="56" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>CD-502</t>
+        </is>
+      </c>
+      <c r="B33" s="40" t="inlineStr">
+        <is>
+          <t>CD-5</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>MODWT translation invariance test</t>
+        </is>
+      </c>
+      <c r="D33" s="35" t="inlineStr">
+        <is>
+          <t>tests/test_decomp.py</t>
+        </is>
+      </c>
+      <c r="E33" s="35" t="inlineStr">
+        <is>
+          <t>shift x by k samples → every component shifts by k</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>CD-102</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>Roll input array by k=17 samples; verify each component shifts by same k. This is the defining property of MODWT vs DWT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="56" customHeight="1">
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>CD-503</t>
+        </is>
+      </c>
+      <c r="B34" s="40" t="inlineStr">
+        <is>
+          <t>CD-5</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>Hurst statistical validation (fGn)</t>
+        </is>
+      </c>
+      <c r="D34" s="35" t="inlineStr">
+        <is>
+          <t>tests/test_hurst.py</t>
+        </is>
+      </c>
+      <c r="E34" s="35" t="inlineStr">
+        <is>
+          <t>fbm.fgn(N=4096, H=h, seed=s),
+50 seeds per H, max_err=0.07</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>CD-107</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>Generate fractional Gaussian noise with known H∈{0.3,0.5,0.7,0.85}. N=4096 samples, 50 seeds. Mean absolute estimation error must be ≤ 0.07 at 95% confidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="56" customHeight="1">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>CD-504</t>
+        </is>
+      </c>
+      <c r="B35" s="40" t="inlineStr">
+        <is>
+          <t>CD-5</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>Wavelet coherence validation</t>
+        </is>
+      </c>
+      <c r="D35" s="35" t="inlineStr">
+        <is>
+          <t>tests/test_coherence.py</t>
+        </is>
+      </c>
+      <c r="E35" s="35" t="inlineStr">
+        <is>
+          <t>shared slow factor + independent fast noise,
+R²&gt;0.5 long scales outside decoupling window,
+R²&lt;0.3 inside</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>CD-108</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>Construct: x = slow_signal + noise_x, y = slow_signal + noise_y. Introduce decoupling window where slow_signal is replaced by independent series. Verify R² thresholds as specified in SRS §5.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="56" customHeight="1">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>CD-505</t>
+        </is>
+      </c>
+      <c r="B36" s="40" t="inlineStr">
+        <is>
+          <t>CD-5</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>Causality / look-ahead tests</t>
+        </is>
+      </c>
+      <c r="D36" s="35" t="inlineStr">
+        <is>
+          <t>tests/test_causality.py</t>
+        </is>
+      </c>
+      <c r="E36" s="35" t="inlineStr">
+        <is>
+          <t>no-leakage swap test,
+look-ahead detector (R²&gt;0.95 sanity check)</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>CD-204</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>No-leakage: swap target at t' &lt; t with noise; predictions at t' must not change. Look-ahead detector: deliberate non-causal forecaster must achieve R²&gt;0.95 OOS — if it doesn't, the test suite itself has a bug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="56" customHeight="1">
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>CD-506</t>
+        </is>
+      </c>
+      <c r="B37" s="40" t="inlineStr">
+        <is>
+          <t>CD-5</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>End-to-end Heston SV path test</t>
+        </is>
+      </c>
+      <c r="D37" s="35" t="inlineStr">
+        <is>
+          <t>tests/test_e2e_heston.py</t>
+        </is>
+      </c>
+      <c r="E37" s="35" t="inlineStr">
+        <is>
+          <t>2500-day Heston SV path,
+HAR R²≥0.85 OOS,
+rolling vol ±30% of target on ≥70% days,
+VMD-HAR RMSE within ±10% of HAR</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>CD-204,CD-501,CD-505</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>Mark @pytest.mark.slow — excluded from quick-test.sh. Generates Heston path with seed for reproducibility. VMD-HAR guard: RMSE within ±10% of HAR catches accidental look-ahead re-introduction.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Chart Decomposition — Architecture &amp; Data Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Component diagram (text) | SRS §2, §3, §4 | 2026-05-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="43" t="inlineStr">
+        <is>
+          <t>1. Component Overview</t>
+        </is>
+      </c>
+      <c r="B4" s="45" t="n"/>
+      <c r="C4" s="45" t="n"/>
+      <c r="D4" s="45" t="n"/>
+      <c r="E4" s="45" t="n"/>
+      <c r="F4" s="46" t="n"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>Python library
+chart_decomp/</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>types.py          ← all dataclass result types
+decomp.py         ← modwt(), emd(), eemd(), vmd()
+time_freq.py      ← cwt_scalogram(), hilbert_spectrum()
+hurst.py          ← hurst_wavelet()
+coherence.py      ← wavelet_coherence()
+realized_vol.py   ← realized_variance(), realized_vol()
+pipelines.py      ← hybrid_a(), hybrid_b(), hybrid_c()
+forecast.py       ← har_forecast(), vmd_har_forecast()
+backtest.py       ← vol_target_backtest()</t>
+        </is>
+      </c>
+      <c r="C5" s="45" t="n"/>
+      <c r="D5" s="45" t="n"/>
+      <c r="E5" s="45" t="n"/>
+      <c r="F5" s="46" t="n"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>FastAPI service
+chart-decomp-service/
+(port 8011)</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>main.py           ← lifespan, /health/*, /metrics
+config.py         ← pydantic-settings
+api/routes.py     ← POST /decompose/*, /hurst, /coherence,
+                     /forecast/*, /backtest/vol-target
+services/         ← thin wrappers calling chart_decomp library
+cli.py            ← chart-decompose CLI entry point
+Dockerfile + requirements.txt</t>
+        </is>
+      </c>
+      <c r="C6" s="45" t="n"/>
+      <c r="D6" s="45" t="n"/>
+      <c r="E6" s="45" t="n"/>
+      <c r="F6" s="46" t="n"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>React frontend
+ChartDecomposition/</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>index.js                ← page layout, tabs
+SeriesInputPanel.js     ← symbol picker + CSV upload
+MODWTBandChart.js       ← stacked band line charts
+CWTScalogram.js         ← heatmap + COI overlay
+HilbertSpectrum.js      ← Hilbert spectrum heatmap
+HurstDiagnostics.js     ← log-log variance + Ĥ readout
+CoherenceHeatmap.js     ← R² heatmap + phase arrows
+ForecastPanel.js        ← HAR vs VMD-HAR line chart
+MetricsTable.js         ← RMSE/MAE/R²/QLIKE/DM table
+BacktestEquityCurve.js  ← net PnL equity curve
+RollingVolChart.js      ← 30d rolling vol vs target
+StrategyMetricsCard.js  ← Sharpe, MaxDD, turnover, cost drag
+chartDecompService.js   ← API wrapper (services/)</t>
+        </is>
+      </c>
+      <c r="C7" s="45" t="n"/>
+      <c r="D7" s="45" t="n"/>
+      <c r="E7" s="45" t="n"/>
+      <c r="F7" s="46" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>2. Data Flow</t>
+        </is>
+      </c>
+      <c r="B9" s="45" t="n"/>
+      <c r="C9" s="45" t="n"/>
+      <c r="D9" s="45" t="n"/>
+      <c r="E9" s="45" t="n"/>
+      <c r="F9" s="46" t="n"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>Decomposition
+request</t>
+        </is>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>Browser → POST /stock_helper/api/v2/chart-decomp/decompose/modwt
+         body: { series: [float, …], wavelet: 'sym8', level: 6 }
+Traefik → chart-decomp-service:8011
+Service → chart_decomp.modwt() → MODWTResult
+Response: { approximation: [], details: [[],[],…], coi_widths: [], wavelet, level }</t>
+        </is>
+      </c>
+      <c r="C10" s="45" t="n"/>
+      <c r="D10" s="45" t="n"/>
+      <c r="E10" s="45" t="n"/>
+      <c r="F10" s="46" t="n"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>Forecast
+request</t>
+        </is>
+      </c>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>Browser → POST /stock_helper/api/v2/chart-decomp/forecast/vmd-har
+         body: { log_rv: [float, …], K: 4, alpha: 1500, window: 1000, … }
+Service → chart_decomp.vmd_har_forecast()  [causal walk-forward]
+Response: ForecastResult { timestamps, predictions, actuals, metrics, features_used }</t>
+        </is>
+      </c>
+      <c r="C11" s="45" t="n"/>
+      <c r="D11" s="45" t="n"/>
+      <c r="E11" s="45" t="n"/>
+      <c r="F11" s="46" t="n"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>Backtest
+request</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>Browser → POST /stock_helper/api/v2/chart-decomp/backtest/vol-target
+         body: { returns: [], vol_forecast: [], target_ann_vol: 0.15, … }
+Service → chart_decomp.vol_target_backtest()
+Response: BacktestResult { pnl_gross, pnl_net, positions, turnover, metrics }</t>
+        </is>
+      </c>
+      <c r="C12" s="45" t="n"/>
+      <c r="D12" s="45" t="n"/>
+      <c r="E12" s="45" t="n"/>
+      <c r="F12" s="46" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>3. Key Design Constraints (from SRS §2.5)</t>
+        </is>
+      </c>
+      <c r="B14" s="45" t="n"/>
+      <c r="C14" s="45" t="n"/>
+      <c r="D14" s="45" t="n"/>
+      <c r="E14" s="45" t="n"/>
+      <c r="F14" s="46" t="n"/>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="A15" s="44" t="inlineStr">
+        <is>
+          <t>C1 Strict causality</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>Forecasting module MUST NOT decompose the full series and slice. Use only data up to prediction time. vmd_har_forecast() applies VMD on a trailing window [t-WINDOW, t]. NFR-R2 raises exception if fit includes future timestamps.</t>
+        </is>
+      </c>
+      <c r="C15" s="45" t="n"/>
+      <c r="D15" s="45" t="n"/>
+      <c r="E15" s="45" t="n"/>
+      <c r="F15" s="46" t="n"/>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="44" t="inlineStr">
+        <is>
+          <t>C2 Boundary handling</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>All time-freq views return COI as a 1-D array. Frontend MUST overlay COI on every CWT scalogram, HHT spectrum, and coherence plot. Do not render edge-contaminated regions as reliable analysis.</t>
+        </is>
+      </c>
+      <c r="C16" s="45" t="n"/>
+      <c r="D16" s="45" t="n"/>
+      <c r="E16" s="45" t="n"/>
+      <c r="F16" s="46" t="n"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="44" t="inlineStr">
+        <is>
+          <t>C3 Mode-ordering stability</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>VMD modes are sorted by ascending center frequency at every call and every refit. Without this, the feature vector silently changes meaning between VMD refits.</t>
+        </is>
+      </c>
+      <c r="C17" s="45" t="n"/>
+      <c r="D17" s="45" t="n"/>
+      <c r="E17" s="45" t="n"/>
+      <c r="F17" s="46" t="n"/>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="A18" s="44" t="inlineStr">
+        <is>
+          <t>C4 Benchmark gating</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>Forecast UI must always show Naive and HAR side-by-side with any candidate model. 'Improves on HAR' label requires ΔRMSE&gt;0 AND ΔQLIKE&gt;0 AND |DM|&gt;1.96.</t>
+        </is>
+      </c>
+      <c r="C18" s="45" t="n"/>
+      <c r="D18" s="45" t="n"/>
+      <c r="E18" s="45" t="n"/>
+      <c r="F18" s="46" t="n"/>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="A19" s="44" t="inlineStr">
+        <is>
+          <t>C5 Reproducibility</t>
+        </is>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>eemd(), synthetic data generators, and Heston SV test all accept seed=. Library logs its version + dependency versions in any saved ForecastResult.</t>
+        </is>
+      </c>
+      <c r="C19" s="45" t="n"/>
+      <c r="D19" s="45" t="n"/>
+      <c r="E19" s="45" t="n"/>
+      <c r="F19" s="46" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="43" t="inlineStr">
+        <is>
+          <t>4. Service Registration Checklist</t>
+        </is>
+      </c>
+      <c r="B21" s="45" t="n"/>
+      <c r="C21" s="45" t="n"/>
+      <c r="D21" s="45" t="n"/>
+      <c r="E21" s="45" t="n"/>
+      <c r="F21" s="46" t="n"/>
+    </row>
+    <row r="22" ht="56" customHeight="1">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>docker-compose.yml</t>
+        </is>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>Add chart-decomp-service block, port 8011, health-check on /health/live</t>
+        </is>
+      </c>
+      <c r="C22" s="45" t="n"/>
+      <c r="D22" s="45" t="n"/>
+      <c r="E22" s="45" t="n"/>
+      <c r="F22" s="46" t="n"/>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>Traefik labels</t>
+        </is>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>PathPrefix=/stock_helper/api/v2/chart-decomp → chart-decomp-service:8011</t>
+        </is>
+      </c>
+      <c r="C23" s="45" t="n"/>
+      <c r="D23" s="45" t="n"/>
+      <c r="E23" s="45" t="n"/>
+      <c r="F23" s="46" t="n"/>
+    </row>
+    <row r="24" ht="56" customHeight="1">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>constants/api.js</t>
+        </is>
+      </c>
+      <c r="B24" s="35" t="inlineStr">
+        <is>
+          <t>Add CHART_DECOMP_BASE and per-endpoint constants</t>
+        </is>
+      </c>
+      <c r="C24" s="45" t="n"/>
+      <c r="D24" s="45" t="n"/>
+      <c r="E24" s="45" t="n"/>
+      <c r="F24" s="46" t="n"/>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>chartDecompService.js</t>
+        </is>
+      </c>
+      <c r="B25" s="35" t="inlineStr">
+        <is>
+          <t>One method per endpoint; wrap httpClient; no axios in components</t>
+        </is>
+      </c>
+      <c r="C25" s="45" t="n"/>
+      <c r="D25" s="45" t="n"/>
+      <c r="E25" s="45" t="n"/>
+      <c r="F25" s="46" t="n"/>
+    </row>
+    <row r="26" ht="56" customHeight="1">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>Sidebar.js</t>
+        </is>
+      </c>
+      <c r="B26" s="35" t="inlineStr">
+        <is>
+          <t>Add nav entry under Analysis group, use i18n key chartDecomp.nav</t>
+        </is>
+      </c>
+      <c r="C26" s="45" t="n"/>
+      <c r="D26" s="45" t="n"/>
+      <c r="E26" s="45" t="n"/>
+      <c r="F26" s="46" t="n"/>
+    </row>
+    <row r="27" ht="56" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>en.json / vi.json</t>
+        </is>
+      </c>
+      <c r="B27" s="35" t="inlineStr">
+        <is>
+          <t>Add chartDecomp.* i18n keys for all labels, tooltips, axis titles</t>
+        </is>
+      </c>
+      <c r="C27" s="45" t="n"/>
+      <c r="D27" s="45" t="n"/>
+      <c r="E27" s="45" t="n"/>
+      <c r="F27" s="46" t="n"/>
+    </row>
+    <row r="28" ht="56" customHeight="1">
+      <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t>CLAUDE.md gateway map</t>
+        </is>
+      </c>
+      <c r="B28" s="35" t="inlineStr">
+        <is>
+          <t>Add /chart-decomp → chart-decomp-service row to routing table</t>
+        </is>
+      </c>
+      <c r="C28" s="45" t="n"/>
+      <c r="D28" s="45" t="n"/>
+      <c r="E28" s="45" t="n"/>
+      <c r="F28" s="46" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B26:F26"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/stockpredict/roadmap_version_2.xlsx
+++ b/stockpredict/roadmap_version_2.xlsx
@@ -1121,6 +1121,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -2091,7 +2092,7 @@
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr"/>
@@ -2134,7 +2135,7 @@
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
@@ -2162,7 +2163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2651,6 +2652,44 @@
           <t>CD-5 test_e2e_heston.py — 2500-day Heston SV path end-to-end test.
 Verify CD-3 and CD-4 pages in browser once backend is running.
 Consider npm run build to check for any remaining import/TS issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CD-5 (CD-506), Phase 6 (C-601/C-602), Polish (snap-to-bar)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CD-506: test_e2e_heston.py — 2500-day Heston SV path, HAR R&gt;=0.85, rolling-vol ±30% on &gt;=70% days (5 pass, 2 VMD-HAR skip/vmdpy absent)
+C-601: Phase 6 comparison overlay — CompReturn % return LineSeries on right Y-axis; alignment by time key; normalization from window start
+C-602: Comparator symbol picker UI — text input + Enter to confirm, ×-button to remove, amber legend strip in header
+Snap-to-bar: snap={true} on TrendLine component
+Bug fix: decomp_service.py VMDResult.omega_final → center_frequencies</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>chart-decomp-lib/tests/test_e2e_heston.py (new)
+stock_react_javascript/src/components/ui/StockChart.js (+comparator input, compLookup, compReturn, Chart id=7)
+stock_microservices/services/chart-decomp-service/app/services/decomp_service.py (omega_final fix)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>CD-5 now fully Done (CD-506 passes). Phase 6 C-601/C-602 implemented in StockChart.js (comparison overlay + symbol picker). Snap-to-bar enabled. Bundle +14.6 kB gzipped.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Verify Phase 6 comparison in browser once backend is running (enter a second ticker, confirm it shows a % return amber line on right Y-axis). Consider per-symbol color palette if multiple comparisons wanted later.</t>
         </is>
       </c>
     </row>
@@ -3077,6 +3116,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3509,6 +3549,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -5186,7 +5227,7 @@
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">

--- a/stockpredict/roadmap_version_2.xlsx
+++ b/stockpredict/roadmap_version_2.xlsx
@@ -1121,7 +1121,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -2163,7 +2162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2690,6 +2689,184 @@
       <c r="F18" t="inlineStr">
         <is>
           <t>Verify Phase 6 comparison in browser once backend is running (enter a second ticker, confirm it shows a % return amber line on right Y-axis). Consider per-symbol color palette if multiple comparisons wanted later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Chart System SRS — Phase 0 (gap analysis)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Read docs/SRS_master_chart_system.md v3.0 (consolidated Part I+II+III) in full.
+Surveyed chart-decomp-lib, chart-decomp-service, and ai-insights-service/patterns.
+Wrote docs/srs_gap_analysis.md mapping every FR-* ID to Implemented/Partial/Not, with file:symbol citations, reuse list, 6 SRS-vs-code conflicts, and dependency check.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>docs/srs_gap_analysis.md (new)
+docs/SRS_master_chart_system.md (spec, already present)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Findings: Part I (FR-DECOMP/TF/HURST/COH/HYB/RV/FCST/BT) essentially fully implemented incl. all mandatory Part I harnesses (round-trip, translation-inv, fGn-Hurst, coherence, no-leakage, look-ahead, e2e Heston) — matches CD-1..CD-5 Done.
+Part II (pattern detection: FR-DN/SW/PAT-EXT/SCORE/FPR/VIZ + II.5 harnesses) NOT implemented per SRS; ai-insights-service/patterns is a parallel OHLC/Schwager detector that violates L2 (hand-rolled swings), L3 (no null-FPR), L4 (pct-of-price thresholds).
+Smaller Part I gaps: chart-decompose CLI is BROKEN (stale API calls); no matplotlib/notebooks (NFR-U2); DM stat not attached to ForecastResult.metrics; Hurst stationary-input not enforced; NFR-P perf budgets unverified.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Phase 1 (design): write docs/design.md for the NOT/PARTIAL items — chiefly the Part II two-layer pipeline (MODWT denoise -&gt; argrelextrema swings -&gt; detector registry -&gt; null-FPR), reusing chart-decomp-lib. Confirm Conflict A (no matplotlib; render in React) and Conflict B (build Part II fresh in chart-decomp-lib, leave ai-insights detectors).
+No CD-6xx pattern tasks exist in this workbook yet; add them in/after design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Chart SRS — Phase 1 (design), Phase 2 (plan), Phase 3/A0 (roadmap rows)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Phase 1: docs/design.md — Part II into chart-decomp-lib DDD layers, reuse MODWT denoise; 6 conflicts resolved (no matplotlib/React render; build fresh leave ai-insights; fix CLI; IPatternDetector; Hurst guard; DM wiring).
+Phase 2: docs/implementation_plan.md — Track A (A1–A17) + Track B (B1–B5), PR-sized, dep graph, mandatory-harness placement.
+Phase 3 A0: CD-601…617 (Part II) + CD-701…705 (clean-ups) added to CD Tasks; CD-6/CD-7 rows in CD Overview; SRS refs repointed to SRS_master_chart_system.md.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>docs/design.md (new)
+docs/implementation_plan.md (new)
+roadmap_version_2.xlsx</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Phases 0–2 done. Roadmap now tracks all Part II + clean-up tasks (CD-6xx/CD-7xx, Not Started).</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Phase 3 task A1 (CD-601): Part II domain types in domain/{entities,value_objects,interfaces}.py + tests/test_pattern_domain.py. Then A2 denoiser (reuse MODWT).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Phase 3 — A1 (CD-601): Part II domain types</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Added Part II domain layer to chart-decomp-lib: entities Swing, SwingSkeleton, Detection, PatternPipelineResult; frozen value objects DenoiseParams/SwingParams/HSParams/FlagParams/TriangleParams/DoubleParams/NullFPRParams; Protocols IDenoiser/ISwingExtractor/IPatternDetector/INullEvaluator. TDD: wrote test_pattern_domain.py first (failed on import), then implemented. 35 new tests pass; full fast suite 73 passed / 12 skipped (optional deps), no regressions.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>chart_decomp/domain/entities.py
+chart_decomp/domain/value_objects.py
+chart_decomp/domain/interfaces.py
+tests/test_pattern_domain.py (new)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>CD-601 Done. Reused existing TimeSeries (no parallel PriceSeries). SRS field names adopted (Conflict C).</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Phase 3 task A2 (CD-602): Layer-1 wavelet denoiser (infrastructure/denoise/wavelet_denoiser.py), reuse MODWT; refactor hybrid_a band-drop. Tests test_denoise.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Phase 3 — A2 (CD-602): Layer-1 wavelet denoiser</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Added infrastructure/denoise/wavelet_denoiser.py (WaveletDenoiser, implements IDenoiser): method='drop' zeroes finest k_drop MODWT detail bands; 'soft'/'hard' apply universal-threshold (σ·√(2lnN), σ from MAD of finest band) shrinkage. Reuses MODWTDecomposer. Refactored hybrid_a to call the denoiser and removed its dead duplicate band-drop block. TDD: test_denoise.py written first (failed on missing module), then implemented — 7 tests pass. Full fast suite 80 passed / 12 skipped (optional deps), no regressions.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>chart_decomp/infrastructure/denoise/__init__.py (new)
+chart_decomp/infrastructure/denoise/wavelet_denoiser.py (new)
+chart_decomp/application/hybrid_pipeline_usecase.py (refactor)
+tests/test_denoise.py (new)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>CD-602 Done. FR-DN-1 satisfied. Denoiser is the single reuse point of Part I's wavelet engine (B5).</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Phase 3 task A3 (CD-603): swing extractor (infrastructure/swings/swing_extractor.py) via scipy.signal.argrelextrema + alternation + prominence + scale-robust thresholds (FR-SW-1/2/3, fixes L2/L4). Tests test_swings.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Phase 3 — A3 (CD-603): Swing extractor</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Added infrastructure/swings/swing_extractor.py (SwingExtractor, implements ISwingExtractor): candidate extrema via scipy.signal.argrelextrema (L2, no hand loop), then a significance ZigZag enforcing strict H/L alternation (FR-SW-2), prominence + min_gap filtering, and scale-robust threshold modes range_frac/atr/absolute (FR-SW-3, L4). Close-only Wilder ATR helper. Lone seed pivot (&lt;2) returns []. TDD: test_swings.py first (failed on missing module); one assertion fixed the impl (drop sub-2 result). 12 tests pass; full fast suite 92 passed / 12 skipped, no regressions.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>chart_decomp/infrastructure/swings/__init__.py (new)
+chart_decomp/infrastructure/swings/swing_extractor.py (new)
+tests/test_swings.py (new)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>CD-603 Done. FR-SW-1/2/3 satisfied; fixes the ai-insights L2 (hand-rolled swings) and L4 (pct-of-price) violations.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Phase 3 task A4 (CD-604): random-walk surrogate generator (infrastructure/validation/surrogates.py), seeded (NFR-RP1), prereq for null-FPR. Tests test_surrogates.py. ∥ could also do A5.</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3112,11 +3289,10 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SRS: SRS_chart_decomposition.md  |  As of 2026-05-27  |  Status: CD-1 Done | CD-2 Done | CD-3 Done | CD-4 Done | CD-5 Partial</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>SRS: SRS_master_chart_system.md  |  As of 2026-05-30 (Part II + clean-ups planned)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3452,54 +3628,129 @@
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="41" t="inlineStr">
-        <is>
-          <t>Total estimate (new module end-to-end)</t>
+      <c r="A10" s="40" t="inlineStr">
+        <is>
+          <t>CD-6</t>
         </is>
       </c>
       <c r="B10" s="45" t="n"/>
       <c r="C10" s="45" t="n"/>
       <c r="D10" s="46" t="n"/>
-      <c r="E10" s="6" t="inlineStr"/>
-      <c r="F10" s="42" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="F10" s="36" t="inlineStr">
+        <is>
+          <t>8–12 days</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Mandatory harnesses: planted, null-FPR, threshold-robust, determinism. docs/implementation_plan.md A1–A17 (CD-601…617).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="inlineStr">
+        <is>
+          <t>CD-7</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Part I Clean-ups</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>• Fix broken chart-decompose CLI
+• Hurst stationary-input guard
+• DM-stat wiring into metrics
+• version provenance
+• (opt) notebooks + viz extra</t>
+        </is>
+      </c>
+      <c r="D11" s="35" t="inlineStr">
+        <is>
+          <t>cli.py, wavelet_hurst.py, run_forecast_usecase.py</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F11" s="36" t="inlineStr">
+        <is>
+          <t>1–2 days</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Independent of Part II; interleave anytime. B1/B2 recommended. CD-701…705.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="41" t="inlineStr">
+        <is>
+          <t>Total estimate (new module end-to-end)</t>
+        </is>
+      </c>
+      <c r="B12" s="45" t="n"/>
+      <c r="C12" s="45" t="n"/>
+      <c r="D12" s="46" t="n"/>
+      <c r="E12" s="6" t="inlineStr"/>
+      <c r="F12" s="42" t="inlineStr">
         <is>
           <t>18–25 days</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Assumes one developer. CD-1 and CD-3 can partially overlap once decomposition API shapes are agreed. CD-5 runs in parallel with CD-4.</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Effort key:</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>S = &lt;2 h</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>M = 2–4 h</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>L = 4–8 h</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>XL = &gt;8 h</t>
         </is>
@@ -3521,7 +3772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3545,11 +3796,10 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ref: SRS_chart_decomposition.md  |  2026-05-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Ref: SRS_master_chart_system.md  |  2026-05-30  |  Part II + clean-ups added (see docs/implementation_plan.md)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -5238,6 +5488,1028 @@
       <c r="I37" s="6" t="inlineStr">
         <is>
           <t>Mark @pytest.mark.slow — excluded from quick-test.sh. Generates Heston path with seed for reproducibility. VMD-HAR guard: RMSE within ±10% of HAR catches accidental look-ahead re-introduction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="23" t="inlineStr">
+        <is>
+          <t>CD-601</t>
+        </is>
+      </c>
+      <c r="B38" s="34" t="inlineStr">
+        <is>
+          <t>CD-6</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>Part II domain types (A1)</t>
+        </is>
+      </c>
+      <c r="D38" s="35" t="inlineStr">
+        <is>
+          <t>domain/entities.py, value_objects.py, interfaces.py</t>
+        </is>
+      </c>
+      <c r="E38" s="35" t="inlineStr">
+        <is>
+          <t>Swing, SwingSkeleton, Detection, PatternPipelineResult;
+DenoiseParams/SwingParams/...; IPatternDetector</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="n"/>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>SRS §II.4 data models. Reuse existing TimeSeries. Frozen-dataclass idiom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>CD-602</t>
+        </is>
+      </c>
+      <c r="B39" s="34" t="inlineStr">
+        <is>
+          <t>CD-6</t>
+        </is>
+      </c>
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>Layer 1 wavelet denoiser (A2)</t>
+        </is>
+      </c>
+      <c r="D39" s="35" t="inlineStr">
+        <is>
+          <t>infrastructure/denoise/wavelet_denoiser.py
+(refactor hybrid_pipeline_usecase)</t>
+        </is>
+      </c>
+      <c r="E39" s="35" t="inlineStr">
+        <is>
+          <t>denoise(): drop / soft / hard</t>
+        </is>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>CD-601</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>FR-DN-1. Reuse MODWT; factor band-drop out of hybrid_a, remove dead block.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>CD-603</t>
+        </is>
+      </c>
+      <c r="B40" s="34" t="inlineStr">
+        <is>
+          <t>CD-6</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>Swing extractor (A3)</t>
+        </is>
+      </c>
+      <c r="D40" s="35" t="inlineStr">
+        <is>
+          <t>infrastructure/swings/swing_extractor.py</t>
+        </is>
+      </c>
+      <c r="E40" s="35" t="inlineStr">
+        <is>
+          <t>scipy.signal.argrelextrema + alternation + prominence</t>
+        </is>
+      </c>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>CD-601</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>FR-SW-1/2/3. Vetted primitive (L2). Range-frac/ATR/absolute thresholds (L4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="23" t="inlineStr">
+        <is>
+          <t>CD-604</t>
+        </is>
+      </c>
+      <c r="B41" s="34" t="inlineStr">
+        <is>
+          <t>CD-6</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>Random-walk surrogate generator (A4)</t>
+        </is>
+      </c>
+      <c r="D41" s="35" t="inlineStr">
+        <is>
+          <t>infrastructure/validation/surrogates.py</t>
+        </is>
+      </c>
+      <c r="E41" s="35" t="inlineStr">
+        <is>
+          <t>random_walk_surrogates(length, vol, n, seed)</t>
+        </is>
+      </c>
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>CD-601</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>Seeded (NFR-RP1). Prereq for null-FPR. ∥ with CD-602.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="23" t="inlineStr">
+        <is>
+          <t>CD-605</t>
+        </is>
+      </c>
+      <c r="B42" s="34" t="inlineStr">
+        <is>
+          <t>CD-6</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>Detector base + registry/factory (A5)</t>
+        </is>
+      </c>
+      <c r="D42" s="35" t="inlineStr">
+        <is>
+          <t>infrastructure/patterns/base.py
+factories/pattern_detector_factory.py</t>
+        </is>
+      </c>
+      <c r="E42" s="35" t="inlineStr">
+        <is>
+          <t>register_detector, detect_patterns</t>
+        </is>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>CD-601</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>FR-PAT-EXT. Mirrors decomposer_factory. Leaves room for FR-ML-1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="23" t="inlineStr">
+        <is>
+          <t>CD-606</t>
+        </is>
+      </c>
+      <c r="B43" s="34" t="inlineStr">
+        <is>
+          <t>CD-6</t>
+        </is>
+      </c>
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>Head &amp; Shoulders detector +inverse (A6)</t>
+        </is>
+      </c>
+      <c r="D43" s="35" t="inlineStr">
+        <is>
+          <t>infrastructure/patterns/head_shoulders.py</t>
+        </is>
+      </c>
+      <c r="E43" s="35" t="inlineStr">
+        <is>
+          <t>FR-PAT-HS</t>
+        </is>
+      </c>
+      <c r="F43" s="24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>CD-603,CD-605</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>Introduces planted-pattern harness (II.5.1 MANDATORY). Harvest geometry from ai-insights.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="23" t="inlineStr">
+        <is>
+          <t>CD-607</t>
+        </is>
+      </c>
+      <c r="B44" s="34" t="inlineStr">
+        <is>
+          <t>CD-6</t>
+        </is>
+      </c>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>Double top/bottom detector (A7)</t>
+        </is>
+      </c>
+      <c r="D44" s="35" t="inlineStr">
+        <is>
+          <t>infrastructure/patterns/double.py</t>
+        </is>
+      </c>
+      <c r="E44" s="35" t="inlineStr">
+        <is>
+          <t>FR-PAT-DT</t>
+        </is>
+      </c>
+      <c r="F44" s="24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>CD-603,CD-605</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>∥ with CD-606/608/609. Extend planted harness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="23" t="inlineStr">
+        <is>
+          <t>CD-608</t>
+        </is>
+      </c>
+      <c r="B45" s="34" t="inlineStr">
+        <is>
+          <t>CD-6</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>Flag / Pennant detector (A8)</t>
+        </is>
+      </c>
+      <c r="D45" s="35" t="inlineStr">
+        <is>
+          <t>infrastructure/patterns/flag_pennant.py</t>
+        </is>
+      </c>
+      <c r="E45" s="35" t="inlineStr">
+        <is>
+          <t>FR-PAT-FLAG</t>
+        </is>
+      </c>
+      <c r="F45" s="24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>CD-603,CD-605</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>∥. Parallel⇒flag, converging⇒pennant via bound-line slope fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="23" t="inlineStr">
+        <is>
+          <t>CD-609</t>
+        </is>
+      </c>
+      <c r="B46" s="34" t="inlineStr">
+        <is>
+          <t>CD-6</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>Triangle detector asc/desc/sym (A9)</t>
+        </is>
+      </c>
+      <c r="D46" s="35" t="inlineStr">
+        <is>
+          <t>infrastructure/patterns/triangle.py</t>
+        </is>
+      </c>
+      <c r="E46" s="35" t="inlineStr">
+        <is>
+          <t>FR-PAT-TRI</t>
+        </is>
+      </c>
+      <c r="F46" s="24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>CD-603,CD-605</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>∥. Slope-pair classification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t>CD-610</t>
+        </is>
+      </c>
+      <c r="B47" s="34" t="inlineStr">
+        <is>
+          <t>CD-6</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>Default registry population (A10)</t>
+        </is>
+      </c>
+      <c r="D47" s="35" t="inlineStr">
+        <is>
+          <t>factories/pattern_detector_factory.py</t>
+        </is>
+      </c>
+      <c r="E47" s="35" t="inlineStr">
+        <is>
+          <t>detect_patterns(...,'all')</t>
+        </is>
+      </c>
+      <c r="F47" s="24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>CD-606,CD-607,CD-608,CD-609</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>Consolidated all-four planted series (II.5.1 end-to-end).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="23" t="inlineStr">
+        <is>
+          <t>CD-611</t>
+        </is>
+      </c>
+      <c r="B48" s="34" t="inlineStr">
+        <is>
+          <t>CD-6</t>
+        </is>
+      </c>
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t>Null-FPR evaluator + significance gate (A11)</t>
+        </is>
+      </c>
+      <c r="D48" s="35" t="inlineStr">
+        <is>
+          <t>infrastructure/validation/null_fpr.py</t>
+        </is>
+      </c>
+      <c r="E48" s="35" t="inlineStr">
+        <is>
+          <t>null_fpr(); 95th-pct noteworthy gate</t>
+        </is>
+      </c>
+      <c r="F48" s="24" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>CD-604,CD-610</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>FR-FPR-1/2. MANDATORY II.5.2. TEST-FIRST vs stub. L3 — the core gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="23" t="inlineStr">
+        <is>
+          <t>CD-612</t>
+        </is>
+      </c>
+      <c r="B49" s="34" t="inlineStr">
+        <is>
+          <t>CD-6</t>
+        </is>
+      </c>
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>End-to-end pipeline + facade (A12)</t>
+        </is>
+      </c>
+      <c r="D49" s="35" t="inlineStr">
+        <is>
+          <t>application/run_pattern_pipeline_usecase.py
+chart_decomp/__init__.py</t>
+        </is>
+      </c>
+      <c r="E49" s="35" t="inlineStr">
+        <is>
+          <t>run_pattern_pipeline, denoise, extract_swings, detect_patterns</t>
+        </is>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>CD-602,CD-603,CD-610,CD-611</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>compute_fpr default on. confirmed=False right-edge flag (B6/C2) via coi_widths.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="23" t="inlineStr">
+        <is>
+          <t>CD-613</t>
+        </is>
+      </c>
+      <c r="B50" s="34" t="inlineStr">
+        <is>
+          <t>CD-6</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>Joint denoise↔swing calibration (A13)</t>
+        </is>
+      </c>
+      <c r="D50" s="35" t="inlineStr">
+        <is>
+          <t>application/denoise_swings_usecase.py</t>
+        </is>
+      </c>
+      <c r="E50" s="35" t="inlineStr">
+        <is>
+          <t>calibrate_denoise_swings()</t>
+        </is>
+      </c>
+      <c r="F50" s="24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>CD-602,CD-603</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>FR-DN-2 (L1 coupling). Recall column when planted labels supplied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="23" t="inlineStr">
+        <is>
+          <t>CD-614</t>
+        </is>
+      </c>
+      <c r="B51" s="34" t="inlineStr">
+        <is>
+          <t>CD-6</t>
+        </is>
+      </c>
+      <c r="C51" s="26" t="inlineStr">
+        <is>
+          <t>Threshold-robustness harness (A14)</t>
+        </is>
+      </c>
+      <c r="D51" s="35" t="inlineStr">
+        <is>
+          <t>tests/test_threshold_robustness.py</t>
+        </is>
+      </c>
+      <c r="E51" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>CD-612</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>II.5.3. Quiet + volatile regime, both planted patterns detected (L4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="23" t="inlineStr">
+        <is>
+          <t>CD-615</t>
+        </is>
+      </c>
+      <c r="B52" s="34" t="inlineStr">
+        <is>
+          <t>CD-6</t>
+        </is>
+      </c>
+      <c r="C52" s="26" t="inlineStr">
+        <is>
+          <t>Determinism harness (A15)</t>
+        </is>
+      </c>
+      <c r="D52" s="35" t="inlineStr">
+        <is>
+          <t>tests/test_pattern_determinism.py</t>
+        </is>
+      </c>
+      <c r="E52" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>CD-611</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>II.5.4 / NFR-RP1. Fixed seed ⇒ identical null_fpr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="23" t="inlineStr">
+        <is>
+          <t>CD-616</t>
+        </is>
+      </c>
+      <c r="B53" s="34" t="inlineStr">
+        <is>
+          <t>CD-6</t>
+        </is>
+      </c>
+      <c r="C53" s="26" t="inlineStr">
+        <is>
+          <t>Service /patterns endpoints (A16)</t>
+        </is>
+      </c>
+      <c r="D53" s="35" t="inlineStr">
+        <is>
+          <t>chart-decomp-service app/api/{routes,schemas}.py
+services/decomp_service.py</t>
+        </is>
+      </c>
+      <c r="E53" s="35" t="inlineStr">
+        <is>
+          <t>/patterns/denoise|swings|detect|pipeline|null-fpr</t>
+        </is>
+      </c>
+      <c r="F53" s="24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>CD-612</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>Reuse MODWTRequest idiom + existing /chart-decomp prefix. No new gateway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="23" t="inlineStr">
+        <is>
+          <t>CD-617</t>
+        </is>
+      </c>
+      <c r="B54" s="34" t="inlineStr">
+        <is>
+          <t>CD-6</t>
+        </is>
+      </c>
+      <c r="C54" s="26" t="inlineStr">
+        <is>
+          <t>Frontend pattern panel (A17)</t>
+        </is>
+      </c>
+      <c r="D54" s="35" t="inlineStr">
+        <is>
+          <t>chartDecompService.js, ChartDecomp page,
+Sidebar.js, en/vi.json, constants/api.js</t>
+        </is>
+      </c>
+      <c r="E54" s="35" t="inlineStr">
+        <is>
+          <t>FR-VIZ-1 three-panel, FR-VIZ-2 report</t>
+        </is>
+      </c>
+      <c r="F54" s="24" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>CD-616</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>Render-in-React (Conflict A). Score + null-FPR percentile in report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="23" t="inlineStr">
+        <is>
+          <t>CD-701</t>
+        </is>
+      </c>
+      <c r="B55" s="34" t="inlineStr">
+        <is>
+          <t>CD-7</t>
+        </is>
+      </c>
+      <c r="C55" s="26" t="inlineStr">
+        <is>
+          <t>Repair chart-decompose CLI (B1)</t>
+        </is>
+      </c>
+      <c r="D55" s="35" t="inlineStr">
+        <is>
+          <t>chart-decomp-service/cli.py</t>
+        </is>
+      </c>
+      <c r="E55" s="35" t="inlineStr">
+        <is>
+          <t>fix stale calls; add decompose/forecast/backtest subcmds</t>
+        </is>
+      </c>
+      <c r="F55" s="24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G55" s="11" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="n"/>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>SRS §I.4.3 — BROKEN today. Recommended. ∥ independent of Part II.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="23" t="inlineStr">
+        <is>
+          <t>CD-702</t>
+        </is>
+      </c>
+      <c r="B56" s="34" t="inlineStr">
+        <is>
+          <t>CD-7</t>
+        </is>
+      </c>
+      <c r="C56" s="26" t="inlineStr">
+        <is>
+          <t>Hurst stationary-input guard (B2)</t>
+        </is>
+      </c>
+      <c r="D56" s="35" t="inlineStr">
+        <is>
+          <t>infrastructure/long_memory/wavelet_hurst.py</t>
+        </is>
+      </c>
+      <c r="E56" s="35" t="inlineStr">
+        <is>
+          <t>warn on non-stationary input</t>
+        </is>
+      </c>
+      <c r="F56" s="24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="n"/>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>FR-HURST / Exp 5 (#1 Hurst bug). Non-binding warning. Recommended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="23" t="inlineStr">
+        <is>
+          <t>CD-703</t>
+        </is>
+      </c>
+      <c r="B57" s="34" t="inlineStr">
+        <is>
+          <t>CD-7</t>
+        </is>
+      </c>
+      <c r="C57" s="26" t="inlineStr">
+        <is>
+          <t>DM-stat wiring into metrics (B3)</t>
+        </is>
+      </c>
+      <c r="D57" s="35" t="inlineStr">
+        <is>
+          <t>application/run_forecast_usecase.py
+/forecast/compare</t>
+        </is>
+      </c>
+      <c r="E57" s="35" t="inlineStr">
+        <is>
+          <t>metrics['dm_vs_har'] via optional baseline</t>
+        </is>
+      </c>
+      <c r="F57" s="24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="n"/>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>FR-FCST-EVAL completeness. Logic already exists. Optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="23" t="inlineStr">
+        <is>
+          <t>CD-704</t>
+        </is>
+      </c>
+      <c r="B58" s="34" t="inlineStr">
+        <is>
+          <t>CD-7</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="inlineStr">
+        <is>
+          <t>NFR-RP2 version provenance (B4)</t>
+        </is>
+      </c>
+      <c r="D58" s="35" t="inlineStr">
+        <is>
+          <t>result serialization</t>
+        </is>
+      </c>
+      <c r="E58" s="35" t="inlineStr">
+        <is>
+          <t>{lib,pywt,numpy,scipy} versions</t>
+        </is>
+      </c>
+      <c r="F58" s="24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="n"/>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>Optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="23" t="inlineStr">
+        <is>
+          <t>CD-705</t>
+        </is>
+      </c>
+      <c r="B59" s="34" t="inlineStr">
+        <is>
+          <t>CD-7</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="inlineStr">
+        <is>
+          <t>Notebooks + optional viz extra (B5)</t>
+        </is>
+      </c>
+      <c r="D59" s="35" t="inlineStr">
+        <is>
+          <t>chart_decomp.viz (matplotlib extra)
+3 notebooks</t>
+        </is>
+      </c>
+      <c r="E59" s="35" t="inlineStr">
+        <is>
+          <t>decomposition / forecasting / pattern</t>
+        </is>
+      </c>
+      <c r="F59" s="24" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G59" s="11" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>CD-612</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>NFR-U2 literal compliance. DECISION-GATED (design §15.1). Default: skip.</t>
         </is>
       </c>
     </row>

--- a/stockpredict/roadmap_version_2.xlsx
+++ b/stockpredict/roadmap_version_2.xlsx
@@ -2162,7 +2162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2867,6 +2867,141 @@
       <c r="F23" t="inlineStr">
         <is>
           <t>Phase 3 task A4 (CD-604): random-walk surrogate generator (infrastructure/validation/surrogates.py), seeded (NFR-RP1), prereq for null-FPR. Tests test_surrogates.py. ∥ could also do A5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Phase 3 — A4 (CD-604): Random-walk surrogate generator</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Added infrastructure/validation/surrogates.py: random_walk_surrogates(length, volatility, n, seed, start) — lazy generator of Gaussian random walks matched to a target's length &amp; per-step vol (prereq for null-FPR / L3); estimate_volatility(x). Single seeded Generator for the whole batch (NFR-RP1 / determinism for II.5.4). TDD: test_surrogates.py first (failed on missing module), then implemented. 10 tests pass; full fast suite 102 passed / 12 skipped, no regressions. Committed Phases 0-2 + A1-A3 on branch feat/chart-pattern-detection (fa0a21cc).</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>chart_decomp/infrastructure/validation/__init__.py (new)
+chart_decomp/infrastructure/validation/surrogates.py (new)
+tests/test_surrogates.py (new)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CD-604 Done. Surrogates ready for the FR-FPR-1 null evaluator (A11). Work now on branch feat/chart-pattern-detection.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Phase 3 task A5 (CD-605): detector base + registry/factory (infrastructure/patterns/base.py, factories/pattern_detector_factory.py) — FR-PAT-EXT. Tests test_pattern_registry.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Phase 3 — A5 (CD-605): Detector base + registry/factory</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Added infrastructure/patterns/base.py (PatternDetectorBase: name + detect contract + shared geometry helpers linfit/line_at/rel_diff/within_tol/series_range/clamp01, harvested from ai-insights and re-expressed scale-robustly for the swing skeleton) and factories/pattern_detector_factory.py (PatternDetectorRegistry + module-level default_registry with register_detector/detect_patterns). FR-PAT-EXT open/closed registry (leaves room for FR-ML-1); mirrors decomposer_factory. detect() aggregates selected detectors sorted by start_index; unknown names raise. TDD: test_pattern_registry.py first (import fail), then impl. 14 tests pass; full fast suite 116 passed / 12 skipped, no regressions.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>chart_decomp/infrastructure/patterns/__init__.py (new)
+chart_decomp/infrastructure/patterns/base.py (new)
+chart_decomp/factories/pattern_detector_factory.py (new)
+tests/test_pattern_registry.py (new)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>CD-605 Done. Registry ready; detectors A6-A9 plug in via register_detector. Base geometry helpers reused by all.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Phase 3 task A6 (CD-606): Head &amp; Shoulders detector +inverse (infrastructure/patterns/head_shoulders.py, FR-PAT-HS). Introduces planted-pattern harness test_patterns_planted.py (II.5.1 MANDATORY).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Phase 3 — A6 (CD-606): Head &amp; Shoulders detector +inverse</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Added infrastructure/patterns/head_shoulders.py: HeadAndShouldersDetector (H L H L H, head strictly highest) and InverseHeadAndShouldersDetector (L H L H L, head lowest); shoulders within tol_shoulder, neckline within tol_neckline (relative/scale-robust). FR-SCORE-1 score blends shoulder symmetry + neckline flatness + head prominence (range-normalized). INTRODUCED the MANDATORY planted-pattern harness tests/test_patterns_planted.py (II.5.1) — planted H&amp;S + inverse recovered near true location (clean + noisy), head-not-highest rejected, &lt;5 pivots rejected, top detector silent on inverse. TDD first. 6 planted tests pass; full fast suite 122 passed / 12 skipped, no regressions.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>chart_decomp/infrastructure/patterns/head_shoulders.py (new)
+tests/test_patterns_planted.py (new — II.5.1 harness)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CD-606 Done. FR-PAT-HS satisfied. Planted harness now live; A7-A9 will extend it. Detectors not yet in default registry (A10).</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Phase 3 task A7 (CD-607): Double top/bottom detector (infrastructure/patterns/double.py, FR-PAT-DT). Extend test_patterns_planted.py. ∥ with A8/A9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Phase 3 — A7 (CD-607): Double top/bottom detector</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Added infrastructure/patterns/double.py: DoubleTopDetector (H L H, two near-equal highs within tol_equal, intervening trough &gt;= min_trough_depth, peaks &gt;= min_separation apart) and DoubleBottomDetector (L H L mirror). FR-SCORE-1 score = peak/low similarity + relative depth. Extended the planted harness test_patterns_planted.py (II.5.1): planted double top/bottom recovered near location, unequal-peaks rejected, shallow-trough rejected (tiny swing threshold), top detector silent on bottom. TDD first. 11 planted tests pass (6 H&amp;S + 5 double); full fast suite 127 passed / 12 skipped, no regressions.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>chart_decomp/infrastructure/patterns/double.py (new)
+tests/test_patterns_planted.py (extended)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>CD-607 Done. FR-PAT-DT satisfied. Detectors still not in default registry (A10).</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Phase 3 task A8 (CD-608): Flag/Pennant detector (infrastructure/patterns/flag_pennant.py, FR-PAT-FLAG) — pole + consolidation, parallel⇒flag / converging⇒pennant. Extend test_patterns_planted.py. ∥ with A9.</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5798,7 @@
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
@@ -5711,7 +5846,7 @@
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
@@ -5758,7 +5893,7 @@
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
@@ -5805,7 +5940,7 @@
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">

--- a/stockpredict/roadmap_version_2.xlsx
+++ b/stockpredict/roadmap_version_2.xlsx
@@ -2162,7 +2162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2180,6 +2180,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -3002,6 +3003,338 @@
       <c r="F27" t="inlineStr">
         <is>
           <t>Phase 3 task A8 (CD-608): Flag/Pennant detector (infrastructure/patterns/flag_pennant.py, FR-PAT-FLAG) — pole + consolidation, parallel⇒flag / converging⇒pennant. Extend test_patterns_planted.py. ∥ with A9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Phase 3 — A8 (CD-608): Flag/Pennant detector</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Added infrastructure/patterns/flag_pennant.py: BullFlagDetector (L→H pole ≥ pole_min×range, ≥2H+2L consolidation pivots; parallel slopes → Bull Flag, converging sl_h&lt;0∧sl_l&gt;0 → Bull Pennant) and BearFlagDetector (H→L pole mirror). _classify_channel() implements FR-PAT-FLAG slope-pair test. _score() FR-SCORE-1 blends pole steepness, tightness, channel quality (range-normalised, L4). Extended test_patterns_planted.py (II.5.1): planted Bull Flag + Bull Pennant + Bear Flag detected near true location (score&gt;0.5); large-retrace rejected; cross-detector silence. 17 planted tests pass; full fast suite 133 passed / 12 skipped, no regressions.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>chart_decomp/infrastructure/patterns/flag_pennant.py (new)
+tests/test_patterns_planted.py (extended with 6 A8 tests)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>CD-608 Done. FR-PAT-FLAG satisfied. Detectors not yet in default registry (A10).</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Phase 3 task A9 (CD-609): Triangle detector asc/desc/sym (infrastructure/patterns/triangle.py, FR-PAT-TRI). Extend test_patterns_planted.py. ∥ with A8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Phase 3 — A9 (CD-609): Triangle detector asc/desc/sym</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Added infrastructure/patterns/triangle.py: SymmetricTriangleDetector (falling H + rising L), AscendingTriangleDetector (flat H + rising L), DescendingTriangleDetector (falling H + flat L). Shared _detect() sliding-window logic: smallest valid window ≥2H+≥2L per starting pivot; _classify() uses slope pair vs flat_slope_eps×(range/span) — scale-robust (L4, FR-PAT-TRI). _r2() for line-fit quality; score = 0.4×shape + 0.3×h_r2 + 0.3×l_r2 (FR-SCORE-1). Extended test_patterns_planted.py (II.5.1): Sym/Asc/Desc planted + detected; cross-detector silence; 2H+1L too-few-pivots rejection. 23 planted tests pass; full fast suite 139 passed / 12 skipped, no regressions.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>chart_decomp/infrastructure/patterns/triangle.py (new)
+tests/test_patterns_planted.py (extended with 6 A9 tests)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>CD-609 Done. FR-PAT-TRI satisfied. Detectors not yet in default registry (A10).</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Phase 3 task A10 (CD-610): Default registry population (factories/pattern_detector_factory.py, detect_patterns(...,"all")). Consolidated all-four planted end-to-end test (II.5.1). Depends on A6-A9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Phase 3 — A10 (CD-610): Default registry population</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Populated default_registry in factories/pattern_detector_factory.py with all 9 built-in detectors (A6-A9): HeadAndShouldersDetector, InverseHeadAndShouldersDetector, DoubleTopDetector, DoubleBottomDetector, BullFlagDetector, BearFlagDetector, SymmetricTriangleDetector, AscendingTriangleDetector, DescendingTriangleDetector. Imports placed after default_registry definition (avoid circular import). Added TestDefaultRegistryEndToEnd to test_patterns_planted.py: II.5.1 consolidated harness — detect_patterns(skeleton, x, "all") finds H&amp;S, Double Top, Bull Flag, Symmetric Triangle in their respective planted series. 41 planted+registry tests pass; full fast suite 143 passed / 12 skipped, no regressions.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>chart_decomp/factories/pattern_detector_factory.py (9 detectors registered)
+tests/test_patterns_planted.py (TestDefaultRegistryEndToEnd, 4 end-to-end tests)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>CD-610 Done. All A6-A9 detectors registered; detect_patterns("all") works end-to-end. Phases A6-A10 of Part II complete.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Phase 3 task A11 (CD-611): Null-FPR evaluator + significance gate (infrastructure/validation/null_fpr.py, FR-FPR-1/2). MANDATORY II.5.2. TEST-FIRST vs stub. Depends on A4 (surrogates) + A10 (registry).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Phase 3 — A11 (CD-611): Null-FPR evaluator + significance gate</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Added infrastructure/validation/null_fpr.py: NullFPRResult dataclass; null_fpr(length, vol, detectors, params, swing_params) — streams n_null surrogates (A4), extracts swings, runs detect_patterns, returns fpr_by_pattern + score_pct95_by_pattern. Deterministic via NullFPRParams.seed (II.5.4 / NFR-RP1). is_noteworthy(detection, null_result) → FR-FPR-2 gate: score &gt; pct95, or pct95 undefined → True. test_null_fpr.py (14 tests): structure, determinism (II.5.4), H&amp;S FPR ceiling &lt; 1.0 on 500-pt random walk (II.5.2), is_noteworthy unit (FR-FPR-2), planted H&amp;S noteworthy (FR-FPR-2). 157 passed / 12 skipped, no regressions, 4.4s.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>chart_decomp/infrastructure/validation/null_fpr.py (new)
+tests/test_null_fpr.py (new, 14 tests)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>CD-611 Done. FR-FPR-1/2 satisfied. II.5.2 MANDATORY test live.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Phase 3 task A12 (CD-612): End-to-end pipeline + facade (application/run_pattern_pipeline_usecase.py, chart_decomp/__init__.py). run_pattern_pipeline, denoise, extract_swings, detect_patterns. compute_fpr default on. confirmed=False right-edge flag (B6/C2). Depends on A2,A3,A10,A11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Phase 3 — A12 (CD-612): End-to-end pipeline + facade</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>application/run_pattern_pipeline_usecase.py: RunPatternPipelineUseCase.execute() — denoise (A2) → extract swings (A3) → detect_patterns (A10) → confirmed=False edge flag via _edge_lag=(2^(k_drop+1)-1)*(L-1) (B6/C2) → null_fpr (A11) with null_percentile annotation. chart_decomp/__init__.py: run_pattern_pipeline() facade + exports. 15 pipeline tests pass; 172 passed / 12 skipped, no regressions.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>chart_decomp/application/run_pattern_pipeline_usecase.py (new)
+chart_decomp/__init__.py (run_pattern_pipeline facade added)
+tests/test_run_pattern_pipeline.py (new, 15 tests)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>CD-612 Done. Full Part II pipeline wired end-to-end.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Next: A13 (CD-613) denoise-swing calibration, or A16 (CD-616) service endpoints, or check if A13-A15 are needed before A16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Phase 3 — A13 (CD-613): Joint denoise-swing calibration + roadmap fix</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>application/denoise_swings_usecase.py: CalibrationPoint, CalibrationResult (as_grid, best_recall), DenoiseSwingtUseCase.calibrate(x, k_drop_values, threshold_values, labeled_swings) — denoise once per k_drop then extract swings per threshold; _recall() counts fraction of planted pivot indices recovered within recovery_tol samples (FR-DN-2 / L1 coupling). calibrate_denoise_swings() convenience function. chart_decomp/__init__.py: exposed calibrate_denoise_swings + CalibrationResult. 17 calibration tests pass; 189 passed / 12 skipped, no regressions. Also fixed roadmap: CD-614 and CD-615 were incorrectly marked Done (files do not exist).</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>chart_decomp/application/denoise_swings_usecase.py (new)
+tests/test_denoise_swing_calibration.py (new, 17 tests)
+chart_decomp/__init__.py (calibrate_denoise_swings facade)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>CD-613 Done. FR-DN-2 satisfied. CD-614/615 reset to Not Started (files missing).</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Next: A14 (CD-614) threshold-robustness harness (tests/test_threshold_robustness.py, II.5.3) or A15 (CD-615) determinism harness (tests/test_pattern_determinism.py, II.5.4/NFR-RP1). Both are small (S effort) and unblocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Phase 3 — A14 (CD-614) + A15 (CD-615): threshold-robustness + determinism harnesses</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>tests/test_threshold_robustness.py (A14, II.5.3, 6 tests): Two-regime series (quiet ±20 + volatile ±100 Double Tops). range_frac=0.08, total range≈100 → threshold=8; quiet swings 20&gt;&gt;8 and volatile 100&gt;&gt;8 → both detected. Also tests absolute-threshold mode (8 units) finds quiet regime. L4 compliance. tests/test_pattern_determinism.py (A15, II.5.4/NFR-RP1, 7 tests): null_fpr fixed-seed identical FPR + pct95 (II.5.4); different seeds give different batches (NFR-RP1); geometric detectors + swing extractor are deterministic; run_pattern_pipeline deterministic with compute_fpr=False and compute_fpr=True+fixed seed. 202 passed / 12 skipped, 12.5s, no regressions.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>tests/test_threshold_robustness.py (new, 6 tests)
+tests/test_pattern_determinism.py (new, 7 tests)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>CD-614 Done (II.5.3). CD-615 Done (II.5.4/NFR-RP1). All A6-A15 complete.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Next: A17 (CD-617) Frontend pattern panel (FR-VIZ-1/2). CD-616 already marked Done in roadmap — check if service endpoints actually exist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Phase 3 — A16 (CD-616) + A17 (CD-617): /patterns endpoints + frontend tab</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>A16: Added PatternDenoise/Swings/Detect/Pipeline/NullFPR req+resp schemas; run_pattern_denoise/swings/detect/pipeline/null_fpr service functions (B6/C2 edge-flag, FPR annotation); POST /patterns/denoise|swings|detect|pipeline|null-fpr routes. A17: CHART_DECOMP_PAT_PIPELINE/NULL_FPR constants; patternPipeline/patternNullFPR service methods; PatternTab component (FR-VIZ-1: 3 panels raw/denoised/skeleton/patterns; FR-VIZ-2: detection report table); patterns tab added to ChartDecomp page (GitBranch icon); chart_decomp.patterns.* i18n keys in en.json + vi.json. React build clean. 202 Python tests pass.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>8 files modified/extended across service + frontend layers</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>CD-616 Done. CD-617 Done. All A6-A17 complete. CD-6 phase fully delivered.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>All CD-6 tasks done. Review CD-7 optional tasks (B1-B5) or move to other phases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Phase CD-7 — B1-B4: CLI repair, Hurst guard, DM-stat, version provenance</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>B1 (CD-701): CLI rewrite — fixed stale cd.modwt(x,params)/hurst_wavelet/cwt_scalogram/result.hurst calls; added SRS §I.4.3 subcommands decompose/forecast/backtest; added patterns (Part II) and versions subcmds. B2 (CD-702): _check_stationarity() in wavelet_hurst.py — UserWarning when std(diff(x))/std(x)&lt;0.5 (price-level non-stationary input, FR-HURST/Exp 5). Non-binding. B3 (CD-703): run_forecast_compare sets har.metrics[dm_vs_har]=None and vmd_har.metrics[dm_vs_har]=dm_stat (FR-FCST-EVAL completeness). B4 (CD-704): __version__=2.0.0 and get_versions() in __init__.py (NFR-RP2 provenance). 202 Python tests pass, no regressions.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>cli.py (rewrite)
+infrastructure/long_memory/wavelet_hurst.py
+services/decomp_service.py
+chart_decomp/__init__.py</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>B1-B4 Done. CD-705 (notebooks) skipped (DECISION-GATED). All CD-7 recommended tasks complete.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>All Chart Decomposition tasks complete (CD-1 through CD-7 B1-B4). Move to other roadmap phases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ROADMAP.xlsx sync + what's-next review</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Updated ROADMAP.xlsx: added 3 Feature Inventory rows (chart-decomp Part I, Part II, PatternTab), 1 Sessions Log row, 1 Roadmap row (Phase 4 Done). Fixed stale statuses: alert evaluation → Done, real LLM → Done, training polling → Done, 7 migration items → Obsolete (Django retired), useRouter roadmap row → Done. All CD-1..CD-7 tasks accounted for in both roadmap files.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>3 open Feature Inventory items; 7 open Roadmap milestones. See ROADMAP.xlsx.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>CD system fully delivered. Move to Phase 3.5 perf targets or Phase 5 growth.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Top candidates: (1) Phase 3.5 performance targets — p99 &lt; 300ms measurement. (2) Prediction-service time series CRUD verification. (3) Simulation dashboard (Partial). (4) Secret store (#24 Partial). (5) Phase 5 mobile-responsive pass.</t>
         </is>
       </c>
     </row>
@@ -5987,7 +6320,7 @@
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
@@ -6034,7 +6367,7 @@
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
@@ -6081,7 +6414,7 @@
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
@@ -6128,7 +6461,7 @@
       </c>
       <c r="G48" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
@@ -6176,7 +6509,7 @@
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
@@ -6223,7 +6556,7 @@
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
@@ -6270,7 +6603,7 @@
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
@@ -6317,7 +6650,7 @@
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
@@ -6365,7 +6698,7 @@
       </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
@@ -6413,7 +6746,7 @@
       </c>
       <c r="G54" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
@@ -6460,7 +6793,7 @@
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H55" s="6" t="n"/>
@@ -6503,7 +6836,7 @@
       </c>
       <c r="G56" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H56" s="6" t="n"/>
@@ -6547,7 +6880,7 @@
       </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H57" s="6" t="n"/>
@@ -6590,7 +6923,7 @@
       </c>
       <c r="G58" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H58" s="6" t="n"/>
@@ -6634,7 +6967,7 @@
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">

--- a/stockpredict/roadmap_version_2.xlsx
+++ b/stockpredict/roadmap_version_2.xlsx
@@ -2180,7 +2180,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -3757,7 +3756,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SRS: SRS_master_chart_system.md  |  As of 2026-05-30 (Part II + clean-ups planned)</t>
+          <t>SRS: SRS_master_chart_system.md  |  As of 2026-06-01  |  Status: CD-1..CD-7 Done (Part I + Part II + clean-ups all shipped)</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4085,7 @@
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -4116,7 +4115,7 @@
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -4162,7 +4161,7 @@
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -4188,7 +4187,7 @@
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
